--- a/simulacaoes_/custo_robustez_C13/simulacao_rho100/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/custo_robustez_C13/simulacao_rho100/pre_sizing_results_optimized.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>d_cm</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>esp_cm</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>bw_cm</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>h_cm</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>esp_tab_cm</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>of_volume_m3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>of_fator_flecha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longarina_g_m</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>longarina_g_v</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longarina_g_f</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>tabuleiro_g_m</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>longarina_g_esp</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>tabuleiro_g_esp</t>
         </is>
@@ -497,2052 +485,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999991997595</v>
+        <v>99.9999965076027</v>
       </c>
       <c r="B2" t="n">
-        <v>154.4301077267345</v>
+        <v>114.0958313789569</v>
       </c>
       <c r="C2" t="n">
-        <v>49.28598131793331</v>
+        <v>45.50070589338263</v>
       </c>
       <c r="D2" t="n">
-        <v>6.141278179110174</v>
+        <v>7.662454308485494</v>
       </c>
       <c r="E2" t="n">
-        <v>4.440667885197606</v>
+        <v>4.842999575556443</v>
       </c>
       <c r="F2" t="n">
-        <v>12.90659098343598</v>
+        <v>13.34988348768848</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02166426146467265</v>
+        <v>0.02080349039236188</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8935251605064281</v>
+        <v>-0.861775044071743</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.931676413413248</v>
+        <v>-0.912999479372905</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9596161242869762</v>
+        <v>-0.9432362679327536</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0007236713762051261</v>
+        <v>-0.001112133352499793</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6190139453926821</v>
+        <v>-0.5499999764263183</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0007946309258344127</v>
+        <v>-0.0001568651961408873</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>46.1383146480177</v>
+        <v>99.9999965076027</v>
       </c>
       <c r="B3" t="n">
-        <v>97.94425323963203</v>
+        <v>112.4025526573605</v>
       </c>
       <c r="C3" t="n">
-        <v>49.29366030586993</v>
+        <v>45.50070589338263</v>
       </c>
       <c r="D3" t="n">
-        <v>7.293795081801226</v>
+        <v>7.662454308485494</v>
       </c>
       <c r="E3" t="n">
-        <v>4.099293818898084</v>
+        <v>4.549627747184617</v>
       </c>
       <c r="F3" t="n">
-        <v>4.823515298535791</v>
+        <v>13.34988348768848</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3344516739749887</v>
+        <v>0.02080349039236188</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00722456872205268</v>
+        <v>-0.861775044071743</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5525861377076193</v>
+        <v>-0.912999479372905</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2228165044176573</v>
+        <v>-0.9432362679327536</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0005083565971067452</v>
+        <v>-0.001112133352499793</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5551337737112081</v>
+        <v>-0.5499999764263183</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.001885531953955919</v>
+        <v>-0.0001568651961408873</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>46.1383146480177</v>
+        <v>50.7407944058935</v>
       </c>
       <c r="B4" t="n">
-        <v>97.94425323963203</v>
+        <v>115.6889610850798</v>
       </c>
       <c r="C4" t="n">
-        <v>49.29366030586993</v>
+        <v>45.62433607192188</v>
       </c>
       <c r="D4" t="n">
-        <v>7.293795081801226</v>
+        <v>11.63702936302068</v>
       </c>
       <c r="E4" t="n">
-        <v>4.099245476174653</v>
+        <v>4.57640404517734</v>
       </c>
       <c r="F4" t="n">
-        <v>4.823515298535791</v>
+        <v>5.422355232942998</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3344516739749887</v>
+        <v>0.2391104082872858</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.00722456872205268</v>
+        <v>-0.01040557651851246</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5525861377076193</v>
+        <v>-0.551661278502489</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2228165044176573</v>
+        <v>-0.2288984408526236</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0005083565971067452</v>
+        <v>-4.713297353552863e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5551337737112081</v>
+        <v>-0.2555559580442013</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.001885531953955919</v>
+        <v>-0.02763023820486335</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99.99999991997595</v>
+        <v>64.73635643665591</v>
       </c>
       <c r="B5" t="n">
-        <v>165.5142942549915</v>
+        <v>135.185951101879</v>
       </c>
       <c r="C5" t="n">
-        <v>49.28598131793331</v>
+        <v>45.50511319422737</v>
       </c>
       <c r="D5" t="n">
-        <v>6.141278179110174</v>
+        <v>11.16452678695826</v>
       </c>
       <c r="E5" t="n">
-        <v>4.223056297122584</v>
+        <v>4.708758549657127</v>
       </c>
       <c r="F5" t="n">
-        <v>12.90659098343598</v>
+        <v>7.22335878779654</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02166426146467265</v>
+        <v>0.09603709617213167</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8935251605064281</v>
+        <v>-0.5119073120615438</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.931676413413248</v>
+        <v>-0.7423708720471336</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9596161242869762</v>
+        <v>-0.6976767117264643</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0007236713762051261</v>
+        <v>-0.02960277434293718</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6190139453926821</v>
+        <v>-0.3119704059474274</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0007946309258344127</v>
+        <v>-0.001136265383860774</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62.69240749775572</v>
+        <v>63.50928044010143</v>
       </c>
       <c r="B6" t="n">
-        <v>108.1414730885598</v>
+        <v>99.47764466134137</v>
       </c>
       <c r="C6" t="n">
-        <v>49.29577157939447</v>
+        <v>45.50067156281964</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0131410494542</v>
+        <v>10.52207718977211</v>
       </c>
       <c r="E6" t="n">
-        <v>4.310691137864663</v>
+        <v>4.627814704696917</v>
       </c>
       <c r="F6" t="n">
-        <v>6.747197641292985</v>
+        <v>6.906198344808002</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1126104299508564</v>
+        <v>0.1025150750150354</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5917545855341017</v>
+        <v>-0.4900279846214</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7780646248452842</v>
+        <v>-0.7345432993444273</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7605057005387263</v>
+        <v>-0.6805494113462209</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01011671447252458</v>
+        <v>-0.0007226019595841786</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3632569427780132</v>
+        <v>-0.3513196033007607</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.002185466069957588</v>
+        <v>-0.0001492361821416044</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55.8673937013528</v>
+        <v>60.77427219218693</v>
       </c>
       <c r="B7" t="n">
-        <v>148.6918536108616</v>
+        <v>104.6418309875705</v>
       </c>
       <c r="C7" t="n">
-        <v>49.30146458435964</v>
+        <v>45.50529919468746</v>
       </c>
       <c r="D7" t="n">
-        <v>10.92266017362849</v>
+        <v>10.77245776982636</v>
       </c>
       <c r="E7" t="n">
-        <v>4.067106162240679</v>
+        <v>4.279572420238599</v>
       </c>
       <c r="F7" t="n">
-        <v>5.911094329046179</v>
+        <v>6.557234113453891</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1747913047871907</v>
+        <v>0.1207646532306125</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4260687081295164</v>
+        <v>-0.4195043404282328</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7072291979576908</v>
+        <v>-0.7053761703161521</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6232271576615418</v>
+        <v>-0.6205745973369434</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01566319045308779</v>
+        <v>-0.0003674761130354605</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2906612003981268</v>
+        <v>-0.330807041441402</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.002994232149661472</v>
+        <v>-0.001177598819434855</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57.75199885357543</v>
+        <v>59.13244876376572</v>
       </c>
       <c r="B8" t="n">
-        <v>180.1821723055426</v>
+        <v>106.9213445487205</v>
       </c>
       <c r="C8" t="n">
-        <v>49.28618040720313</v>
+        <v>45.50168807183208</v>
       </c>
       <c r="D8" t="n">
-        <v>10.70204007885828</v>
+        <v>11.20729807397916</v>
       </c>
       <c r="E8" t="n">
-        <v>4.09852348058961</v>
+        <v>4.62586730380001</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1131668636845</v>
+        <v>6.41416901986063</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1540930711996204</v>
+        <v>0.1341104593123138</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4796242253642455</v>
+        <v>-0.3705039276390916</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7294161373893917</v>
+        <v>-0.6856315929893331</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6692389873585197</v>
+        <v>-0.5774029700811418</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.004241107589758636</v>
+        <v>-0.0505001068392279</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3046829255574728</v>
+        <v>-0.3184933657282429</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.000822914169790138</v>
+        <v>-0.0003751270737967216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>59.71727935539231</v>
+        <v>89.06775830209052</v>
       </c>
       <c r="B9" t="n">
-        <v>149.6979113122815</v>
+        <v>84.04005808711139</v>
       </c>
       <c r="C9" t="n">
-        <v>49.28241118771477</v>
+        <v>45.57419476210057</v>
       </c>
       <c r="D9" t="n">
-        <v>10.74540221791201</v>
+        <v>9.581429440713494</v>
       </c>
       <c r="E9" t="n">
-        <v>4.95461914523684</v>
+        <v>4.615596425470478</v>
       </c>
       <c r="F9" t="n">
-        <v>6.390390293723676</v>
+        <v>11.31091938339543</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1360946104576566</v>
+        <v>0.03082327965734244</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5282527306957104</v>
+        <v>-0.8072696774718505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7500356086990994</v>
+        <v>-0.8824562752136177</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7096403982781837</v>
+        <v>-0.9118563707605933</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.04295548581481608</v>
+        <v>-0.1522015721474224</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3193048865687747</v>
+        <v>-0.4762073685391111</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0002874470680046259</v>
+        <v>-0.01648772491123898</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>50.14328149559276</v>
+        <v>69.36732491535558</v>
       </c>
       <c r="B10" t="n">
-        <v>86.85894283211213</v>
+        <v>91.00268089486647</v>
       </c>
       <c r="C10" t="n">
-        <v>49.29366030586993</v>
+        <v>45.64770125880625</v>
       </c>
       <c r="D10" t="n">
-        <v>7.42313287186261</v>
+        <v>10.1139602223757</v>
       </c>
       <c r="E10" t="n">
-        <v>4.099293818898084</v>
+        <v>4.531457072822088</v>
       </c>
       <c r="F10" t="n">
-        <v>5.448143031177948</v>
+        <v>7.746354335189359</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2443561933997161</v>
+        <v>0.07420021259768191</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2234167125690364</v>
+        <v>-0.6062193237169036</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6304589177181934</v>
+        <v>-0.7850695907909517</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.439248996848483</v>
+        <v>-0.7733530089114184</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1512650628352522</v>
+        <v>-0.03405116723854843</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5816204509362368</v>
+        <v>-0.3952549368651668</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.001885531953955919</v>
+        <v>-0.03282250195694503</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>82.25533273087692</v>
+        <v>95.1696069098771</v>
       </c>
       <c r="B11" t="n">
-        <v>148.1856732252371</v>
+        <v>83.94340910127232</v>
       </c>
       <c r="C11" t="n">
-        <v>49.28296304689039</v>
+        <v>45.50117130475893</v>
       </c>
       <c r="D11" t="n">
-        <v>8.554511105032889</v>
+        <v>8.371759948029492</v>
       </c>
       <c r="E11" t="n">
-        <v>4.719140045687299</v>
+        <v>4.395637836782196</v>
       </c>
       <c r="F11" t="n">
-        <v>9.651775985012064</v>
+        <v>12.38448805488351</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04232555090103091</v>
+        <v>0.02454954981289079</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8143554535296307</v>
+        <v>-0.840779479535534</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.886620402412801</v>
+        <v>-0.9009833959556249</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9157506685608449</v>
+        <v>-0.9315595857554452</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.04749499412837335</v>
+        <v>-0.0416367009838167</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4869911468366155</v>
+        <v>-0.5173948466416706</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0003658459074130556</v>
+        <v>-0.0002602899464278219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96.84062655952197</v>
+        <v>67.2162856914923</v>
       </c>
       <c r="B12" t="n">
-        <v>142.9357898810143</v>
+        <v>107.6149119705437</v>
       </c>
       <c r="C12" t="n">
-        <v>49.28612150243493</v>
+        <v>45.51302571402948</v>
       </c>
       <c r="D12" t="n">
-        <v>7.419193556128986</v>
+        <v>11.20102560714735</v>
       </c>
       <c r="E12" t="n">
-        <v>4.143075434325857</v>
+        <v>4.269149524445451</v>
       </c>
       <c r="F12" t="n">
-        <v>12.45081084823216</v>
+        <v>7.616744140562708</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02419675951277748</v>
+        <v>0.08376386413068145</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8833440485035773</v>
+        <v>-0.5627975562119415</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9257311300311137</v>
+        <v>-0.7644181520257513</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9544286160018343</v>
+        <v>-0.7387894410944169</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2115932522461092</v>
+        <v>-0.0709855435564536</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5955077669850725</v>
+        <v>-0.3287099284175731</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0008145459743033768</v>
+        <v>-0.002894603117661876</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>47.33280309799716</v>
+        <v>86.71648806388619</v>
       </c>
       <c r="B13" t="n">
-        <v>97.94425323963203</v>
+        <v>79.45610219413592</v>
       </c>
       <c r="C13" t="n">
-        <v>49.29366030586993</v>
+        <v>45.64200538799279</v>
       </c>
       <c r="D13" t="n">
-        <v>7.284842894180819</v>
+        <v>9.532367238234256</v>
       </c>
       <c r="E13" t="n">
-        <v>4.140186702415526</v>
+        <v>4.468206364146207</v>
       </c>
       <c r="F13" t="n">
-        <v>4.994675276803027</v>
+        <v>10.81683954247323</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3035428522209229</v>
+        <v>0.0337573295364915</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.07946354466272186</v>
+        <v>-0.7918929889910705</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5780302523403363</v>
+        <v>-0.8742576276141885</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.297082124354333</v>
+        <v>-0.9024319547370905</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0340684918773423</v>
+        <v>-0.09926650020990135</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5630334720677095</v>
+        <v>-0.4603362944312317</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.001885531953955919</v>
+        <v>-0.03155675288728579</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>49.70625751617347</v>
+        <v>66.42094955069625</v>
       </c>
       <c r="B14" t="n">
-        <v>105.3984774702791</v>
+        <v>95.23963491442517</v>
       </c>
       <c r="C14" t="n">
-        <v>49.29985484182381</v>
+        <v>46.75791389288461</v>
       </c>
       <c r="D14" t="n">
-        <v>7.130767567915275</v>
+        <v>10.12719599323144</v>
       </c>
       <c r="E14" t="n">
-        <v>4.601508439829979</v>
+        <v>4.708606403618543</v>
       </c>
       <c r="F14" t="n">
-        <v>5.283935387656005</v>
+        <v>7.32833124354959</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2523727629987129</v>
+        <v>0.08697378705131817</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2032128913470782</v>
+        <v>-0.5528455767349193</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6229544016302327</v>
+        <v>-0.7614250272698512</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4198150749975741</v>
+        <v>-0.7317018869770359</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01167266899756684</v>
+        <v>-0.004373622212360259</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5676800780573532</v>
+        <v>-0.3731571216302219</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.002765547093527076</v>
+        <v>-0.2795364206410251</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>84.17254474895854</v>
+        <v>56.42042273107171</v>
       </c>
       <c r="B15" t="n">
-        <v>145.7940935703858</v>
+        <v>113.3845583176879</v>
       </c>
       <c r="C15" t="n">
-        <v>49.44737656390122</v>
+        <v>45.50165914329433</v>
       </c>
       <c r="D15" t="n">
-        <v>8.614795822477415</v>
+        <v>11.47233343440334</v>
       </c>
       <c r="E15" t="n">
-        <v>4.993926093180581</v>
+        <v>4.936676842556344</v>
       </c>
       <c r="F15" t="n">
-        <v>10.04124933182468</v>
+        <v>6.099240592778676</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03910090746231697</v>
+        <v>0.1600871442428268</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8261720333362669</v>
+        <v>-0.2768984331055121</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8930528326038688</v>
+        <v>-0.6491053341457362</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9227699518164838</v>
+        <v>-0.4918960278781689</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1102646599797925</v>
+        <v>-0.01116276098371173</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5012554716253024</v>
+        <v>-0.2769955119588859</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.02372294403341021</v>
+        <v>-0.0003686985098498574</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>48.9726203535621</v>
+        <v>72.79981081695044</v>
       </c>
       <c r="B16" t="n">
-        <v>104.2521423717869</v>
+        <v>87.98383020412624</v>
       </c>
       <c r="C16" t="n">
-        <v>49.30152102418629</v>
+        <v>45.55935791651491</v>
       </c>
       <c r="D16" t="n">
-        <v>7.029921584023478</v>
+        <v>9.663940998877413</v>
       </c>
       <c r="E16" t="n">
-        <v>4.981666361037605</v>
+        <v>4.421364173916073</v>
       </c>
       <c r="F16" t="n">
-        <v>5.186372009669959</v>
+        <v>8.224967713576492</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2664886922512278</v>
+        <v>0.06221862665873853</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1677870555262435</v>
+        <v>-0.6580713477518474</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6099645208463744</v>
+        <v>-0.8088616921054773</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3853315060320036</v>
+        <v>-0.8120735034385707</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01610676004521201</v>
+        <v>-0.01212052307480621</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5738783334633735</v>
+        <v>-0.4209985811271283</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.003002250167847618</v>
+        <v>-0.01319064811442616</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>46.60000869739497</v>
+        <v>92.88344082388954</v>
       </c>
       <c r="B17" t="n">
-        <v>98.15370519578659</v>
+        <v>104.6418309875705</v>
       </c>
       <c r="C17" t="n">
-        <v>49.33253917048525</v>
+        <v>45.5006965082443</v>
       </c>
       <c r="D17" t="n">
-        <v>7.293795081801226</v>
+        <v>8.566006109653447</v>
       </c>
       <c r="E17" t="n">
-        <v>4.099293818898084</v>
+        <v>4.241719871493617</v>
       </c>
       <c r="F17" t="n">
-        <v>4.891073375441464</v>
+        <v>11.91775452155533</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3220612168784419</v>
+        <v>0.0266417898034612</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.03601194206456702</v>
+        <v>-0.8293090440379364</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5626588770082079</v>
+        <v>-0.8945771107527304</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2526314637616199</v>
+        <v>-0.9249616277483732</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01516548046342696</v>
+        <v>-0.0296590342409438</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.558187167591354</v>
+        <v>-0.5019632255612545</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.007408784983008217</v>
+        <v>-0.0001547796098436138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>65.39961489390711</v>
+        <v>96.79084611570778</v>
       </c>
       <c r="B18" t="n">
-        <v>155.4786807830873</v>
+        <v>98.67745587538779</v>
       </c>
       <c r="C18" t="n">
-        <v>49.28819600400133</v>
+        <v>45.50080363780708</v>
       </c>
       <c r="D18" t="n">
-        <v>10.08088130382131</v>
+        <v>8.024716748945318</v>
       </c>
       <c r="E18" t="n">
-        <v>4.303343494842583</v>
+        <v>4.62762308001257</v>
       </c>
       <c r="F18" t="n">
-        <v>7.078137267540714</v>
+        <v>12.68005598878772</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09685487211154195</v>
+        <v>0.02318397533099648</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6388164755324793</v>
+        <v>-0.8483144495101032</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7993149796921579</v>
+        <v>-0.9052635982065668</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.79636577700985</v>
+        <v>-0.9358141510861017</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01419537620489035</v>
+        <v>-0.001416756773843922</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3615822554331613</v>
+        <v>-0.5283382112810275</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.001109256150995626</v>
+        <v>-0.000178586179351431</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80.39280215873811</v>
+        <v>61.9006506826487</v>
       </c>
       <c r="B19" t="n">
-        <v>149.1058439339186</v>
+        <v>117.5413617530147</v>
       </c>
       <c r="C19" t="n">
-        <v>49.28296304689039</v>
+        <v>45.86139658957606</v>
       </c>
       <c r="D19" t="n">
-        <v>8.617055960553708</v>
+        <v>11.46676609054558</v>
       </c>
       <c r="E19" t="n">
-        <v>4.719140045687299</v>
+        <v>4.555169654633656</v>
       </c>
       <c r="F19" t="n">
-        <v>9.312735522357709</v>
+        <v>6.880572669583159</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04585331952260482</v>
+        <v>0.1135397576715953</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.801742077812846</v>
+        <v>-0.4428540240042511</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8798409495699698</v>
+        <v>-0.7133019029560835</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9080906562793675</v>
+        <v>-0.6395231917634642</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.01601716186691296</v>
+        <v>-0.04917437886169593</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4731336596316114</v>
+        <v>-0.2928293921078787</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0003658459074130556</v>
+        <v>-0.08031035323912444</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>58.30486562324728</v>
+        <v>58.49251092598757</v>
       </c>
       <c r="B20" t="n">
-        <v>144.4147062073933</v>
+        <v>105.8081663914527</v>
       </c>
       <c r="C20" t="n">
-        <v>49.28615810101073</v>
+        <v>45.50716508247302</v>
       </c>
       <c r="D20" t="n">
-        <v>10.94866631002349</v>
+        <v>10.98764596996613</v>
       </c>
       <c r="E20" t="n">
-        <v>4.279854493594553</v>
+        <v>4.89998674582955</v>
       </c>
       <c r="F20" t="n">
-        <v>6.239284305668518</v>
+        <v>6.280785874385895</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1490246254410383</v>
+        <v>0.1393946286206823</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4937316874754933</v>
+        <v>-0.3501726438864315</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.735287996508871</v>
+        <v>-0.6776212488035572</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6810567522517957</v>
+        <v>-0.5592045228579505</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.05681325418484277</v>
+        <v>-0.001977350285914553</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3087963314265651</v>
+        <v>-0.3136938319449067</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0008197452823759443</v>
+        <v>-0.001592240549561086</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>64.70027719496636</v>
+        <v>55.81552311702157</v>
       </c>
       <c r="B21" t="n">
-        <v>175.7985970105091</v>
+        <v>113.3845583176879</v>
       </c>
       <c r="C21" t="n">
-        <v>49.28819600400133</v>
+        <v>46.13964842603571</v>
       </c>
       <c r="D21" t="n">
-        <v>10.08088130382131</v>
+        <v>11.41532938865353</v>
       </c>
       <c r="E21" t="n">
-        <v>4.638379938390197</v>
+        <v>4.559062871197797</v>
       </c>
       <c r="F21" t="n">
-        <v>6.972384963246599</v>
+        <v>6.04035868301346</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1007389611596942</v>
+        <v>0.1668198292177838</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6273091593087938</v>
+        <v>-0.2534462924876508</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7940351194369769</v>
+        <v>-0.6401550764818051</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7877128992238444</v>
+        <v>-0.4698636736070311</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001760574285589312</v>
+        <v>-0.006381295124147905</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3563790854234899</v>
+        <v>-0.2726856022087787</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.001109256150995626</v>
+        <v>-0.1421440946746025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>52.11815784915312</v>
+        <v>52.44004466385624</v>
       </c>
       <c r="B22" t="n">
-        <v>90.50729635052107</v>
+        <v>113.2970272098338</v>
       </c>
       <c r="C22" t="n">
-        <v>49.82900563290088</v>
+        <v>45.50048898919626</v>
       </c>
       <c r="D22" t="n">
-        <v>6.807796956048558</v>
+        <v>11.51357193935704</v>
       </c>
       <c r="E22" t="n">
-        <v>4.041072713611173</v>
+        <v>4.90628390315099</v>
       </c>
       <c r="F22" t="n">
-        <v>5.642578064754781</v>
+        <v>5.597147468557528</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2107307183144725</v>
+        <v>0.2108049063927787</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3074142978612978</v>
+        <v>-0.1024681440817736</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6624069867748302</v>
+        <v>-0.5843985449636837</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5184530618623105</v>
+        <v>-0.3228220872904567</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.06938843447080026</v>
+        <v>-0.001001656492445944</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5946812113686899</v>
+        <v>-0.2683003349789218</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.03925112213864712</v>
+        <v>-0.0001086642658360004</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>93.68878644085976</v>
+        <v>78.95444917463072</v>
       </c>
       <c r="B23" t="n">
-        <v>94.10426822279476</v>
+        <v>77.79119521600335</v>
       </c>
       <c r="C23" t="n">
-        <v>49.28792065558248</v>
+        <v>45.50023397103432</v>
       </c>
       <c r="D23" t="n">
-        <v>7.302928248785503</v>
+        <v>9.667476738170564</v>
       </c>
       <c r="E23" t="n">
-        <v>4.137557892928904</v>
+        <v>4.876545429297965</v>
       </c>
       <c r="F23" t="n">
-        <v>11.72857497118069</v>
+        <v>9.323454590089273</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0269985285425121</v>
+        <v>0.04671373166372051</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8719735088978332</v>
+        <v>-0.7298226280422307</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9191087441989754</v>
+        <v>-0.8433044364117959</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9484736967378196</v>
+        <v>-0.8624566003744881</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.07999978930196319</v>
+        <v>-0.1405718829132293</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5720576369469785</v>
+        <v>-0.4671583688097305</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.001070139293970225</v>
+        <v>-5.199356318291715e-05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51.2536382364878</v>
+        <v>54.14669860888688</v>
       </c>
       <c r="B24" t="n">
-        <v>104.4377283116207</v>
+        <v>113.2970272098338</v>
       </c>
       <c r="C24" t="n">
-        <v>49.3314949507874</v>
+        <v>45.50072110993689</v>
       </c>
       <c r="D24" t="n">
-        <v>7.016507097669589</v>
+        <v>11.4889067150443</v>
       </c>
       <c r="E24" t="n">
-        <v>4.601030714717016</v>
+        <v>4.528026145427287</v>
       </c>
       <c r="F24" t="n">
-        <v>5.500846227961017</v>
+        <v>5.806412975782543</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2247736588274883</v>
+        <v>0.1868061118812253</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2721442237577315</v>
+        <v>-0.1835438391456258</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6488447300432765</v>
+        <v>-0.6139933584600316</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4855594633171059</v>
+        <v>-0.4029097009597755</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.03040036790468049</v>
+        <v>-0.02213236639850854</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5779587494469982</v>
+        <v>-0.2811002395666515</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.007260439868865141</v>
+        <v>-0.0001602466526423596</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55.19852869847892</v>
+        <v>53.30103771707734</v>
       </c>
       <c r="B25" t="n">
-        <v>154.8531250193006</v>
+        <v>114.5980056035124</v>
       </c>
       <c r="C25" t="n">
-        <v>49.30111175789598</v>
+        <v>45.50826840660252</v>
       </c>
       <c r="D25" t="n">
-        <v>10.93659865771494</v>
+        <v>11.48079377816278</v>
       </c>
       <c r="E25" t="n">
-        <v>4.966277074830036</v>
+        <v>4.473619715759381</v>
       </c>
       <c r="F25" t="n">
-        <v>5.827645097334595</v>
+        <v>5.698094707260344</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1828959204693504</v>
+        <v>0.1981953850872386</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4053491054282219</v>
+        <v>-0.1446837207267811</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.698814174985774</v>
+        <v>-0.5997139743002311</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6050452946014574</v>
+        <v>-0.3648407150089796</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.008038910371686433</v>
+        <v>-0.008309735163975497</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2856847514969115</v>
+        <v>-0.2747577828780801</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.002944108519421792</v>
+        <v>-0.001837423689449724</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67.55685424530122</v>
+        <v>51.11145952460996</v>
       </c>
       <c r="B26" t="n">
-        <v>191.7673196516574</v>
+        <v>117.2172557998355</v>
       </c>
       <c r="C26" t="n">
-        <v>49.28899472705818</v>
+        <v>45.50210609590636</v>
       </c>
       <c r="D26" t="n">
-        <v>9.942610890416953</v>
+        <v>11.63768137852997</v>
       </c>
       <c r="E26" t="n">
-        <v>4.258983050943002</v>
+        <v>4.231230210288467</v>
       </c>
       <c r="F26" t="n">
-        <v>7.382649910702067</v>
+        <v>5.460564764052077</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08596723333321613</v>
+        <v>0.2325422106327668</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6714814456716868</v>
+        <v>-0.03153309309832881</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8145673551793419</v>
+        <v>-0.5590947790431544</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8204391685770965</v>
+        <v>-0.2507199601846328</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.02609749460856607</v>
+        <v>-0.002887154167262805</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.3776324170558761</v>
+        <v>-0.2583359464345747</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.001222725244982338</v>
+        <v>-0.0004680213125236865</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87.45464536897002</v>
+        <v>77.87461437709104</v>
       </c>
       <c r="B27" t="n">
-        <v>134.452850234919</v>
+        <v>87.88598374094622</v>
       </c>
       <c r="C27" t="n">
-        <v>49.28296304689039</v>
+        <v>45.50208988329149</v>
       </c>
       <c r="D27" t="n">
-        <v>8.617055960553708</v>
+        <v>9.639638860387576</v>
       </c>
       <c r="E27" t="n">
-        <v>4.793538953787726</v>
+        <v>4.577412363672374</v>
       </c>
       <c r="F27" t="n">
-        <v>10.69044858106135</v>
+        <v>9.11832510581019</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03428274734554839</v>
+        <v>0.04901541068358189</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8441383952976701</v>
+        <v>-0.7188395853442953</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9030415591876003</v>
+        <v>-0.8378989599788451</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.933148193905696</v>
+        <v>-0.8550021984118833</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1874586305469328</v>
+        <v>-0.03080882412261113</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5256747579595485</v>
+        <v>-0.4298566274367736</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0003658459074130556</v>
+        <v>-0.0004644185092195219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>47.7218102235942</v>
+        <v>76.75346085259704</v>
       </c>
       <c r="B28" t="n">
-        <v>104.3740927982902</v>
+        <v>82.58359686408994</v>
       </c>
       <c r="C28" t="n">
-        <v>49.28851471838865</v>
+        <v>45.57805404976377</v>
       </c>
       <c r="D28" t="n">
-        <v>7.128451344701945</v>
+        <v>9.478467598455374</v>
       </c>
       <c r="E28" t="n">
-        <v>4.993063217325451</v>
+        <v>4.880795510498761</v>
       </c>
       <c r="F28" t="n">
-        <v>5.019137850558935</v>
+        <v>8.884326809138209</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2940074395221983</v>
+        <v>0.05153449416580679</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1016316444887097</v>
+        <v>-0.706806197380668</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5859812966223104</v>
+        <v>-0.8320445575241012</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.319531147055634</v>
+        <v>-0.8467280907117487</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.003439661832345828</v>
+        <v>-0.05964550202509194</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5656061540813355</v>
+        <v>-0.4506509563944778</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.00115453371304946</v>
+        <v>-0.01734534439194885</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>71.09031088537179</v>
+        <v>54.89406667713854</v>
       </c>
       <c r="B29" t="n">
-        <v>101.7413911463967</v>
+        <v>111.7686552574002</v>
       </c>
       <c r="C29" t="n">
-        <v>49.31008156566233</v>
+        <v>45.50143656472753</v>
       </c>
       <c r="D29" t="n">
-        <v>9.551612413136272</v>
+        <v>11.29912420101287</v>
       </c>
       <c r="E29" t="n">
-        <v>4.874983886156826</v>
+        <v>4.96594794460164</v>
       </c>
       <c r="F29" t="n">
-        <v>7.926651267539295</v>
+        <v>5.863598137539924</v>
       </c>
       <c r="G29" t="n">
-        <v>0.07119306310485982</v>
+        <v>0.1771439279427025</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7169997544842022</v>
+        <v>-0.2161112836433118</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8365302575493665</v>
+        <v>-0.6261420313707826</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8527030944443048</v>
+        <v>-0.4343910715893854</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0471301651104497</v>
+        <v>-0.0006207231999994493</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.4146141255062499</v>
+        <v>-0.286705500078539</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.004218387447207173</v>
+        <v>-0.0003192366061174901</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>53.36160551187876</v>
+        <v>61.29264342623921</v>
       </c>
       <c r="B30" t="n">
-        <v>106.4344739157473</v>
+        <v>114.0958313789569</v>
       </c>
       <c r="C30" t="n">
-        <v>49.28787914367084</v>
+        <v>45.50080688601455</v>
       </c>
       <c r="D30" t="n">
-        <v>7.922398623485254</v>
+        <v>11.46676609054558</v>
       </c>
       <c r="E30" t="n">
-        <v>4.954490799405954</v>
+        <v>4.768187731948793</v>
       </c>
       <c r="F30" t="n">
-        <v>5.795086922447268</v>
+        <v>6.773723748713812</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1956365455089147</v>
+        <v>0.1176692785875032</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3518300365491573</v>
+        <v>-0.4265466666369437</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6792325965340461</v>
+        <v>-0.7066254288943665</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5587200661314476</v>
+        <v>-0.6254568029749692</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.03112057734918858</v>
+        <v>-0.03355700319313879</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.5260225080890988</v>
+        <v>-0.2887253431271147</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.001064241982050338</v>
+        <v>-0.0001793080032340411</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>92.3050871642358</v>
+        <v>57.50328551157219</v>
       </c>
       <c r="B31" t="n">
-        <v>168.8302045767877</v>
+        <v>106.9213445487205</v>
       </c>
       <c r="C31" t="n">
-        <v>49.28603874957236</v>
+        <v>45.50168807183208</v>
       </c>
       <c r="D31" t="n">
-        <v>7.413339574936671</v>
+        <v>11.20857889866618</v>
       </c>
       <c r="E31" t="n">
-        <v>4.143075434325857</v>
+        <v>4.624075052795638</v>
       </c>
       <c r="F31" t="n">
-        <v>11.45245575292857</v>
+        <v>6.190570827801788</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02839170486887565</v>
+        <v>0.1487955389129773</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8664633325074299</v>
+        <v>-0.316518187266698</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9158973316492923</v>
+        <v>-0.6644222841818915</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9455222220549846</v>
+        <v>-0.5285889730485721</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.06179235309091394</v>
+        <v>-0.02525213510334171</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5617627213583604</v>
+        <v>-0.3062746413367914</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0008027898439890823</v>
+        <v>-0.0003751270737967216</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>53.94873009695344</v>
+        <v>82.49528361819831</v>
       </c>
       <c r="B32" t="n">
-        <v>193.5138348031176</v>
+        <v>91.82659557202913</v>
       </c>
       <c r="C32" t="n">
-        <v>49.28738699848799</v>
+        <v>45.50135050985726</v>
       </c>
       <c r="D32" t="n">
-        <v>11.00188744847516</v>
+        <v>9.530100114147602</v>
       </c>
       <c r="E32" t="n">
-        <v>4.90904704624938</v>
+        <v>4.0470774086999</v>
       </c>
       <c r="F32" t="n">
-        <v>5.68209828474363</v>
+        <v>9.968853517429876</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1994619137130757</v>
+        <v>0.04007050926330172</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3637863260527862</v>
+        <v>-0.7597322890600157</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6821597436245954</v>
+        <v>-0.85755011438842</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.56793300073863</v>
+        <v>-0.8819847163097383</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0007839855220025144</v>
+        <v>-0.01414801866759661</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.2763860756047979</v>
+        <v>-0.4318431644228387</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0009943262991007618</v>
+        <v>-0.0003001133016151958</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>72.45810473423518</v>
+        <v>51.78390099859977</v>
       </c>
       <c r="B33" t="n">
-        <v>198.1629585944227</v>
+        <v>117.5384012575644</v>
       </c>
       <c r="C33" t="n">
-        <v>49.83613903263584</v>
+        <v>45.50024231235829</v>
       </c>
       <c r="D33" t="n">
-        <v>9.304098479303107</v>
+        <v>11.61223926451446</v>
       </c>
       <c r="E33" t="n">
-        <v>4.400660289225552</v>
+        <v>4.876321052969057</v>
       </c>
       <c r="F33" t="n">
-        <v>8.061069665321837</v>
+        <v>5.536771711527805</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0665212889456432</v>
+        <v>0.2212688464797467</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.73218076127486</v>
+        <v>-0.06830120381482659</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8440134967011602</v>
+        <v>-0.5721353609467722</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8630748799460238</v>
+        <v>-0.2883116530220571</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.001400046781154085</v>
+        <v>-0.008287560836624202</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.4140984042213532</v>
+        <v>-0.2633792574894983</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.03909343555322134</v>
+        <v>-5.384719073159294e-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>48.40346314148309</v>
+        <v>90.85018828667128</v>
       </c>
       <c r="B34" t="n">
-        <v>104.1315656596494</v>
+        <v>85.31841181308857</v>
       </c>
       <c r="C34" t="n">
-        <v>49.29224429463527</v>
+        <v>45.50074003021965</v>
       </c>
       <c r="D34" t="n">
-        <v>7.293795081801226</v>
+        <v>8.976313163800858</v>
       </c>
       <c r="E34" t="n">
-        <v>4.232670573042306</v>
+        <v>4.562703160892216</v>
       </c>
       <c r="F34" t="n">
-        <v>5.155354609331003</v>
+        <v>11.56165805640738</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2789373542436678</v>
+        <v>0.02874653663899845</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1382913913450065</v>
+        <v>-0.8180622515445731</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5991650002180492</v>
+        <v>-0.8883646086450266</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3561516756712721</v>
+        <v>-0.9183432884025647</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.06860663448576496</v>
+        <v>-0.07173166606106487</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.570114236545627</v>
+        <v>-0.4882387709350311</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.001684368972000759</v>
+        <v>-0.0001644511599209475</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>48.1975170452422</v>
+        <v>84.66256219788217</v>
       </c>
       <c r="B35" t="n">
-        <v>104.4043718914188</v>
+        <v>91.82659557202913</v>
       </c>
       <c r="C35" t="n">
-        <v>49.28851471838865</v>
+        <v>45.50135050985726</v>
       </c>
       <c r="D35" t="n">
-        <v>7.128451344701945</v>
+        <v>9.530100114147602</v>
       </c>
       <c r="E35" t="n">
-        <v>4.981063966659139</v>
+        <v>4.0470774086999</v>
       </c>
       <c r="F35" t="n">
-        <v>5.089852631881446</v>
+        <v>10.3956517819371</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2831882564949019</v>
+        <v>0.03664205658979677</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1275602427942375</v>
+        <v>-0.7770429830092112</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5953129169595403</v>
+        <v>-0.8664739012582432</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3455107487698335</v>
+        <v>-0.893110952314547</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.01841782985749277</v>
+        <v>-0.05621670264653518</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5687522208325156</v>
+        <v>-0.4464722948357046</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.00115453371304946</v>
+        <v>-0.0003001133016151958</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>75.15317337708274</v>
+        <v>73.3784255779765</v>
       </c>
       <c r="B36" t="n">
-        <v>191.7673196516574</v>
+        <v>114.2679019249899</v>
       </c>
       <c r="C36" t="n">
-        <v>49.28899017749725</v>
+        <v>45.77549425248953</v>
       </c>
       <c r="D36" t="n">
-        <v>9.961058105988915</v>
+        <v>10.48285704378506</v>
       </c>
       <c r="E36" t="n">
-        <v>4.247627338879249</v>
+        <v>4.268128238164211</v>
       </c>
       <c r="F36" t="n">
-        <v>8.646543027737145</v>
+        <v>8.502699791333249</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05862025242853628</v>
+        <v>0.0608224514930789</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7587929303236201</v>
+        <v>-0.662001584346402</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8573143611976732</v>
+        <v>-0.8095945651643175</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8807797785836829</v>
+        <v>-0.8144068930177538</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.1679382795392104</v>
+        <v>-0.0441479014194763</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.4341500907780906</v>
+        <v>-0.3703043726513414</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.001222078920136826</v>
+        <v>-0.06122094499767292</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>61.14495665033007</v>
+        <v>52.76859438663975</v>
       </c>
       <c r="B37" t="n">
-        <v>197.5036942422134</v>
+        <v>113.2970272098338</v>
       </c>
       <c r="C37" t="n">
-        <v>49.2807824699802</v>
+        <v>45.5007054215331</v>
       </c>
       <c r="D37" t="n">
-        <v>10.51078523420364</v>
+        <v>11.51357193935704</v>
       </c>
       <c r="E37" t="n">
-        <v>4.183465399582661</v>
+        <v>4.248701446765338</v>
       </c>
       <c r="F37" t="n">
-        <v>6.541852838680828</v>
+        <v>5.637881108660547</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1244465066407277</v>
+        <v>0.2058951327670165</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5600039078089545</v>
+        <v>-0.1188893025130705</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7638594764203077</v>
+        <v>-0.5903291423488756</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7353283007753542</v>
+        <v>-0.3392437722006886</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.02321800620460537</v>
+        <v>-0.00587694729770174</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.3299270047468169</v>
+        <v>-0.2707644578997981</v>
       </c>
       <c r="M37" t="n">
-        <v>-5.606633582680801e-05</v>
+        <v>-0.0001567603406880946</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>51.44122496682132</v>
+        <v>55.17421669732963</v>
       </c>
       <c r="B38" t="n">
-        <v>104.2521423717869</v>
+        <v>113.3289551294293</v>
       </c>
       <c r="C38" t="n">
-        <v>49.30152102418629</v>
+        <v>45.50048698624079</v>
       </c>
       <c r="D38" t="n">
-        <v>7.029921584023478</v>
+        <v>11.51357193935704</v>
       </c>
       <c r="E38" t="n">
-        <v>4.929830251225739</v>
+        <v>4.90628390315099</v>
       </c>
       <c r="F38" t="n">
-        <v>5.53233552604997</v>
+        <v>5.943785872477035</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2217277806581873</v>
+        <v>0.1741115873789819</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2799255386243844</v>
+        <v>-0.2276042328828019</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6518050962033897</v>
+        <v>-0.6304122420289784</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4928518513945314</v>
+        <v>-0.4453482638333464</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.03960685642571438</v>
+        <v>-0.000637828827231058</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5792048179373467</v>
+        <v>-0.2681162939684736</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.003002250167847618</v>
+        <v>-0.0001082191646178954</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>77.69798510652183</v>
+        <v>85.65141418165091</v>
       </c>
       <c r="B39" t="n">
-        <v>153.9622440981282</v>
+        <v>84.12938577393257</v>
       </c>
       <c r="C39" t="n">
-        <v>49.28605049977921</v>
+        <v>45.50471788396048</v>
       </c>
       <c r="D39" t="n">
-        <v>8.990903481046132</v>
+        <v>9.639638860387576</v>
       </c>
       <c r="E39" t="n">
-        <v>4.601168340255128</v>
+        <v>4.563451380295612</v>
       </c>
       <c r="F39" t="n">
-        <v>8.895795336329162</v>
+        <v>10.61663619390126</v>
       </c>
       <c r="G39" t="n">
-        <v>0.05178973357788992</v>
+        <v>0.03522926637151121</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7812085581926824</v>
+        <v>-0.784337987411865</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8689802379795551</v>
+        <v>-0.8702708884574817</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8952670187655934</v>
+        <v>-0.8977128093946055</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.03590941692052896</v>
+        <v>-0.09632399921605396</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.4530838449442576</v>
+        <v>-0.4531470457261436</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.0008044591151018058</v>
+        <v>-0.001048418657884354</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>69.22652240830848</v>
+        <v>70.59217209984514</v>
       </c>
       <c r="B40" t="n">
-        <v>162.0422557347817</v>
+        <v>90.63086827341395</v>
       </c>
       <c r="C40" t="n">
-        <v>49.2923581743831</v>
+        <v>45.7863895686375</v>
       </c>
       <c r="D40" t="n">
-        <v>9.935249254628562</v>
+        <v>10.48285704378506</v>
       </c>
       <c r="E40" t="n">
-        <v>3.736486052359492</v>
+        <v>4.540300317131257</v>
       </c>
       <c r="F40" t="n">
-        <v>7.646707202905701</v>
+        <v>8.030633500254366</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07868541203599297</v>
+        <v>0.06986052162592594</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6939992772161151</v>
+        <v>-0.6256858394716295</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8252896189819022</v>
+        <v>-0.7938492813996564</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8365769229588577</v>
+        <v>-0.788072528745508</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.05527333954888321</v>
+        <v>-0.1250985856352963</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.390054981040373</v>
+        <v>-0.4044412907488386</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.001700547084925524</v>
+        <v>-0.06364212636388838</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>69.8334685361132</v>
+        <v>80.4842965215981</v>
       </c>
       <c r="B41" t="n">
-        <v>101.7413911463967</v>
+        <v>84.23623158190821</v>
       </c>
       <c r="C41" t="n">
-        <v>49.31008156566233</v>
+        <v>45.50095274129649</v>
       </c>
       <c r="D41" t="n">
-        <v>9.551612413136272</v>
+        <v>9.476748122230983</v>
       </c>
       <c r="E41" t="n">
-        <v>4.874983886156826</v>
+        <v>4.8956318194379</v>
       </c>
       <c r="F41" t="n">
-        <v>7.718839362576699</v>
+        <v>9.571791234913324</v>
       </c>
       <c r="G41" t="n">
-        <v>0.07591249802860521</v>
+        <v>0.04364133945330787</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7019684894260299</v>
+        <v>-0.7444426813585502</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8292174015718288</v>
+        <v>-0.8505987290305289</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8422425552704614</v>
+        <v>-0.8722310368315259</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02236661817668486</v>
+        <v>-0.05132766298310198</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4052950024418298</v>
+        <v>-0.4484506127163864</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.004218387447207173</v>
+        <v>-0.0002117202881078695</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>73.85273472748712</v>
+        <v>75.40387383632086</v>
       </c>
       <c r="B42" t="n">
-        <v>95.42138542809317</v>
+        <v>82.63971569408567</v>
       </c>
       <c r="C42" t="n">
-        <v>49.28358519272793</v>
+        <v>46.54885197651311</v>
       </c>
       <c r="D42" t="n">
-        <v>9.067977851711696</v>
+        <v>9.671110128595506</v>
       </c>
       <c r="E42" t="n">
-        <v>4.871485894013666</v>
+        <v>4.229185867669031</v>
       </c>
       <c r="F42" t="n">
-        <v>8.294293102673299</v>
+        <v>8.724165398210019</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0619203417351991</v>
+        <v>0.05499509865695688</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.746771345131528</v>
+        <v>-0.6912194222367427</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.8513705934840132</v>
+        <v>-0.8245061456087781</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8729035282411034</v>
+        <v>-0.8358249756361038</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.002868089756992319</v>
+        <v>-0.08767946299665431</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.4350967005531098</v>
+        <v>-0.4405290537724065</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0004542298897048251</v>
+        <v>-0.2330782170029125</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>91.08828829241601</v>
+        <v>51.59971212284464</v>
       </c>
       <c r="B43" t="n">
-        <v>113.3718931081771</v>
+        <v>117.4323445982566</v>
       </c>
       <c r="C43" t="n">
-        <v>49.41201136085935</v>
+        <v>45.50023723167626</v>
       </c>
       <c r="D43" t="n">
-        <v>7.476901899838761</v>
+        <v>11.61307814645985</v>
       </c>
       <c r="E43" t="n">
-        <v>4.982735774907648</v>
+        <v>4.899899320062934</v>
       </c>
       <c r="F43" t="n">
-        <v>11.21035731326793</v>
+        <v>5.514509748943858</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02969858256545269</v>
+        <v>0.2242724788065324</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.8613425386276192</v>
+        <v>-0.05842731550421065</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.9129282167839488</v>
+        <v>-0.5686206479036072</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.942743582749087</v>
+        <v>-0.278265632664449</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.04089115359800052</v>
+        <v>-0.005745919853149289</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5527095680573955</v>
+        <v>-0.2619978409213348</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.01869885274996358</v>
+        <v>-5.271815027935167e-05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>61.14495665033007</v>
+        <v>70.52317809059181</v>
       </c>
       <c r="B44" t="n">
-        <v>195.2451063038669</v>
+        <v>90.62211075281171</v>
       </c>
       <c r="C44" t="n">
-        <v>49.2807824699802</v>
+        <v>45.6465249265625</v>
       </c>
       <c r="D44" t="n">
-        <v>10.51078523420364</v>
+        <v>10.48285704378506</v>
       </c>
       <c r="E44" t="n">
-        <v>4.116528050018081</v>
+        <v>4.531858224878984</v>
       </c>
       <c r="F44" t="n">
-        <v>6.541852838680828</v>
+        <v>8.01256559671836</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1244465066407277</v>
+        <v>0.07009141949239811</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.5600039078089545</v>
+        <v>-0.6246278654757863</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.7638594764203077</v>
+        <v>-0.793369990802649</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.7353283007753542</v>
+        <v>-0.7872793206653881</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.02321800620460537</v>
+        <v>-0.1212190206814597</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.3299270047468169</v>
+        <v>-0.4039238356794386</v>
       </c>
       <c r="M44" t="n">
-        <v>-5.606633582680801e-05</v>
+        <v>-0.03256109479166616</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>89.26445987745922</v>
+        <v>74.5704697227735</v>
       </c>
       <c r="B45" t="n">
-        <v>143.9561792412527</v>
+        <v>81.99252360894992</v>
       </c>
       <c r="C45" t="n">
-        <v>49.28239214176966</v>
+        <v>47.16903648514165</v>
       </c>
       <c r="D45" t="n">
-        <v>7.582773017444692</v>
+        <v>9.671110128595506</v>
       </c>
       <c r="E45" t="n">
-        <v>4.81115493048292</v>
+        <v>4.045828235583905</v>
       </c>
       <c r="F45" t="n">
-        <v>10.84604601705732</v>
+        <v>8.60390635204155</v>
       </c>
       <c r="G45" t="n">
-        <v>0.03181226932920634</v>
+        <v>0.05724957121035425</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8531472950900701</v>
+        <v>-0.6810534506155997</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.9082267272112977</v>
+        <v>-0.8196490401012237</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9382274596478147</v>
+        <v>-0.8286183286876535</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.007881859307727829</v>
+        <v>-0.08270932190532577</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5391400302992239</v>
+        <v>-0.4342785229208012</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0002847413415114556</v>
+        <v>-0.3708969966981452</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>99.41173161242659</v>
+        <v>91.96489388134665</v>
       </c>
       <c r="B46" t="n">
-        <v>150.7403723976524</v>
+        <v>84.09058037046334</v>
       </c>
       <c r="C46" t="n">
-        <v>49.28578973717664</v>
+        <v>45.86995202841973</v>
       </c>
       <c r="D46" t="n">
-        <v>6.236581370189535</v>
+        <v>8.665771298525412</v>
       </c>
       <c r="E46" t="n">
-        <v>4.429365012197899</v>
+        <v>4.431128480774402</v>
       </c>
       <c r="F46" t="n">
-        <v>12.79015301618501</v>
+        <v>11.75254989672688</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02209426003458796</v>
+        <v>0.02756328845617958</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.8917435736518152</v>
+        <v>-0.8243547637152974</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9306446880212544</v>
+        <v>-0.8918310936960375</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9587210569605461</v>
+        <v>-0.9220637643613719</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.003778515053471761</v>
+        <v>-0.03803039070809235</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.6146371471446869</v>
+        <v>-0.4957630336990899</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0007674143647274219</v>
+        <v>-0.082211561871052</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>75.4054396082189</v>
+        <v>57.66585386175041</v>
       </c>
       <c r="B47" t="n">
-        <v>154.8386335032839</v>
+        <v>106.9213445487205</v>
       </c>
       <c r="C47" t="n">
-        <v>49.28907484778958</v>
+        <v>45.50168807183208</v>
       </c>
       <c r="D47" t="n">
-        <v>10.08088130382131</v>
+        <v>11.20857889866618</v>
       </c>
       <c r="E47" t="n">
-        <v>4.219821190292119</v>
+        <v>4.623847892390534</v>
       </c>
       <c r="F47" t="n">
-        <v>8.715734367829452</v>
+        <v>6.21262817402951</v>
       </c>
       <c r="G47" t="n">
-        <v>0.05797024263304078</v>
+        <v>0.1472386490590211</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7610703963019328</v>
+        <v>-0.3221801794793172</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8584606553937315</v>
+        <v>-0.6666245395784539</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8822635989162093</v>
+        <v>-0.5337704786990846</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.1920350618132342</v>
+        <v>-0.0277933043019553</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.4360269867187621</v>
+        <v>-0.3074939039631281</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.001234107446514502</v>
+        <v>-0.0003751270737967216</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>78.59004703453661</v>
+        <v>81.30461777242115</v>
       </c>
       <c r="B48" t="n">
-        <v>99.22956869109518</v>
+        <v>78.24202011931126</v>
       </c>
       <c r="C48" t="n">
-        <v>49.28699272932914</v>
+        <v>45.54485701109712</v>
       </c>
       <c r="D48" t="n">
-        <v>8.990903481046132</v>
+        <v>9.482756217046269</v>
       </c>
       <c r="E48" t="n">
-        <v>4.6830832324987</v>
+        <v>4.566636444505114</v>
       </c>
       <c r="F48" t="n">
-        <v>9.057880381141269</v>
+        <v>9.731250671031118</v>
       </c>
       <c r="G48" t="n">
-        <v>0.04975211405643666</v>
+        <v>0.04213303247821768</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.7882777879989914</v>
+        <v>-0.751815679364694</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.8726773700089544</v>
+        <v>-0.8543083428266988</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.8997243722449357</v>
+        <v>-0.8770889872747404</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.05583261494517024</v>
+        <v>-0.0703889933252401</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.4597209100955377</v>
+        <v>-0.4542954016285008</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0009383151900472934</v>
+        <v>-0.009968224688249316</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>90.37864928263916</v>
+        <v>98.36548523194527</v>
       </c>
       <c r="B49" t="n">
-        <v>112.9999234244312</v>
+        <v>112.9465896820662</v>
       </c>
       <c r="C49" t="n">
-        <v>49.28615878083733</v>
+        <v>45.50116320627902</v>
       </c>
       <c r="D49" t="n">
-        <v>7.433113688718882</v>
+        <v>7.868860486901653</v>
       </c>
       <c r="E49" t="n">
-        <v>4.993660372012001</v>
+        <v>4.772078561928847</v>
       </c>
       <c r="F49" t="n">
-        <v>11.04753766877281</v>
+        <v>13.01018680556619</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0304834434069234</v>
+        <v>0.02197238018460881</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8582485634277578</v>
+        <v>-0.8551331821037191</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9111540058114306</v>
+        <v>-0.9091616967948465</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9410501588096837</v>
+        <v>-0.9396018542417796</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.003993361563073171</v>
+        <v>-0.006300814294502767</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.547429754858484</v>
+        <v>-0.5389670253156307</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0008198418606668145</v>
+        <v>-0.0002584902842268921</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>85.73118689799992</v>
+        <v>98.36548523194527</v>
       </c>
       <c r="B50" t="n">
-        <v>134.452850234919</v>
+        <v>86.22331698930579</v>
       </c>
       <c r="C50" t="n">
-        <v>49.29605976664752</v>
+        <v>45.50116320627902</v>
       </c>
       <c r="D50" t="n">
-        <v>8.606889845871043</v>
+        <v>7.868860486901653</v>
       </c>
       <c r="E50" t="n">
-        <v>4.867274423928875</v>
+        <v>4.769823339668307</v>
       </c>
       <c r="F50" t="n">
-        <v>10.34187434506372</v>
+        <v>13.01018680556619</v>
       </c>
       <c r="G50" t="n">
-        <v>0.03670059591829317</v>
+        <v>0.02197238018460881</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8350483118360306</v>
+        <v>-0.8551331821037191</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8979595453463104</v>
+        <v>-0.9091616967948465</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.927944041511778</v>
+        <v>-0.9396018542417796</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.1438369936020239</v>
+        <v>-0.006300814294502767</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.5128519865822184</v>
+        <v>-0.5389670253156307</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.002226406851899225</v>
+        <v>-0.0002584902842268921</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>97.1313897613627</v>
+        <v>53.77081141387596</v>
       </c>
       <c r="B51" t="n">
-        <v>142.9357898810143</v>
+        <v>113.3517550136208</v>
       </c>
       <c r="C51" t="n">
-        <v>49.28611228603846</v>
+        <v>45.50087746965555</v>
       </c>
       <c r="D51" t="n">
-        <v>7.437640773235002</v>
+        <v>11.48672855009933</v>
       </c>
       <c r="E51" t="n">
-        <v>3.966823340464013</v>
+        <v>4.845478229771037</v>
       </c>
       <c r="F51" t="n">
-        <v>12.52022040604742</v>
+        <v>5.75818578065141</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02395965847721759</v>
+        <v>0.1917615864348316</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.8843198463934872</v>
+        <v>-0.1665710219033741</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9262931112616961</v>
+        <v>-0.6077336212794707</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9549311027041095</v>
+        <v>-0.3863544915163225</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.2249520761192844</v>
+        <v>-0.01616829160242681</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5976710857565688</v>
+        <v>-0.2782810856040697</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0008132366642130629</v>
+        <v>-0.0001949932567883728</v>
       </c>
     </row>
   </sheetData>

--- a/simulacaoes_/custo_robustez_C13/simulacao_rho100/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/custo_robustez_C13/simulacao_rho100/pre_sizing_results_optimized.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,67 +429,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>d_cm</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>esp_cm</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>bw_cm</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>h_cm</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>esp_tab_cm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>of_volume_m3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>of_fator_flecha</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_m</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_v</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_f</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tabuleiro_g_m</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_esp</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tabuleiro_g_esp</t>
         </is>
@@ -485,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.9999965076027</v>
+        <v>50.68718030842577</v>
       </c>
       <c r="B2" t="n">
-        <v>114.0958313789569</v>
+        <v>117.8023249730055</v>
       </c>
       <c r="C2" t="n">
-        <v>45.50070589338263</v>
+        <v>45.50299967859524</v>
       </c>
       <c r="D2" t="n">
-        <v>7.662454308485494</v>
+        <v>11.65840470005512</v>
       </c>
       <c r="E2" t="n">
-        <v>4.842999575556443</v>
+        <v>4.800035846700152</v>
       </c>
       <c r="F2" t="n">
-        <v>13.34988348768848</v>
+        <v>5.413971686785674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02080349039236188</v>
+        <v>0.2400495509737423</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.861775044071743</v>
+        <v>-0.007316173561624558</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.912999479372905</v>
+        <v>-0.5505811238609897</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9432362679327536</v>
+        <v>-0.2256981970702278</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.001112133352499793</v>
+        <v>-0.0003016778178485613</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5499999764263183</v>
+        <v>-0.2551538523131933</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0001568651961408873</v>
+        <v>-0.0006665952433845823</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.9999965076027</v>
+        <v>99.99999996294376</v>
       </c>
       <c r="B3" t="n">
-        <v>112.4025526573605</v>
+        <v>62.18811805606081</v>
       </c>
       <c r="C3" t="n">
-        <v>45.50070589338263</v>
+        <v>45.50056322938575</v>
       </c>
       <c r="D3" t="n">
-        <v>7.662454308485494</v>
+        <v>7.679634146865924</v>
       </c>
       <c r="E3" t="n">
-        <v>4.549627747184617</v>
+        <v>4.213784739975689</v>
       </c>
       <c r="F3" t="n">
-        <v>13.34988348768848</v>
+        <v>13.35339699808166</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02080349039236188</v>
+        <v>0.02080472913021237</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.861775044071743</v>
+        <v>-0.8617722050424953</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.912999479372905</v>
+        <v>-0.9129965531427384</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9432362679327536</v>
+        <v>-0.9432344737335115</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.001112133352499793</v>
+        <v>-0.005565808568066257</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5499999764263183</v>
+        <v>-0.5499999997498703</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0001568651961408873</v>
+        <v>-0.0001251620857224689</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50.7407944058935</v>
+        <v>60.39235394910975</v>
       </c>
       <c r="B4" t="n">
-        <v>115.6889610850798</v>
+        <v>110.2100976075242</v>
       </c>
       <c r="C4" t="n">
-        <v>45.62433607192188</v>
+        <v>45.85426092952952</v>
       </c>
       <c r="D4" t="n">
-        <v>11.63702936302068</v>
+        <v>11.06731513654263</v>
       </c>
       <c r="E4" t="n">
-        <v>4.57640404517734</v>
+        <v>2.870321690555036</v>
       </c>
       <c r="F4" t="n">
-        <v>5.422355232942998</v>
+        <v>6.580475175603739</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2391104082872858</v>
+        <v>0.1239800809026454</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01040557651851246</v>
+        <v>-0.4083987018229803</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.551661278502489</v>
+        <v>-0.7008239121269512</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2288984408526236</v>
+        <v>-0.6108614884754529</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.713297353552863e-05</v>
+        <v>-0.005799128640518699</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2555559580442013</v>
+        <v>-0.3052955218874069</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.02763023820486335</v>
+        <v>-0.07872465100656006</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64.73635643665591</v>
+        <v>76.91513871834947</v>
       </c>
       <c r="B5" t="n">
-        <v>135.185951101879</v>
+        <v>79.04541580602546</v>
       </c>
       <c r="C5" t="n">
-        <v>45.50511319422737</v>
+        <v>45.5029322445748</v>
       </c>
       <c r="D5" t="n">
-        <v>11.16452678695826</v>
+        <v>9.307518009444463</v>
       </c>
       <c r="E5" t="n">
-        <v>4.708758549657127</v>
+        <v>4.725109558339248</v>
       </c>
       <c r="F5" t="n">
-        <v>7.22335878779654</v>
+        <v>8.875388050550857</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09603709617213167</v>
+        <v>0.05109792193308252</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5119073120615438</v>
+        <v>-0.7086330741270579</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7423708720471336</v>
+        <v>-0.8329443343514691</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6976767117264643</v>
+        <v>-0.8479978619269775</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02960277434293718</v>
+        <v>-0.02692089716388712</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3119704059474274</v>
+        <v>-0.451863540387621</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.001136265383860774</v>
+        <v>-0.0006516099055113578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63.50928044010143</v>
+        <v>58.56112241330228</v>
       </c>
       <c r="B6" t="n">
-        <v>99.47764466134137</v>
+        <v>116.1828755254681</v>
       </c>
       <c r="C6" t="n">
-        <v>45.50067156281964</v>
+        <v>45.50855151910574</v>
       </c>
       <c r="D6" t="n">
-        <v>10.52207718977211</v>
+        <v>11.61830821094693</v>
       </c>
       <c r="E6" t="n">
-        <v>4.627814704696917</v>
+        <v>3.93816001834107</v>
       </c>
       <c r="F6" t="n">
-        <v>6.906198344808002</v>
+        <v>6.419468351531187</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1025150750150354</v>
+        <v>0.1394987480885184</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4900279846214</v>
+        <v>-0.3439608459958126</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7345432993444273</v>
+        <v>-0.6734132526273652</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6805494113462209</v>
+        <v>-0.5521072101475406</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0007226019595841786</v>
+        <v>-0.0229079550003306</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3513196033007607</v>
+        <v>-0.2702875762897903</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0001492361821416044</v>
+        <v>-0.001900337579053835</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60.77427219218693</v>
+        <v>79.43594406611057</v>
       </c>
       <c r="B7" t="n">
-        <v>104.6418309875705</v>
+        <v>79.04672769226067</v>
       </c>
       <c r="C7" t="n">
-        <v>45.50529919468746</v>
+        <v>45.57152561229663</v>
       </c>
       <c r="D7" t="n">
-        <v>10.77245776982636</v>
+        <v>9.308576266245831</v>
       </c>
       <c r="E7" t="n">
-        <v>4.279572420238599</v>
+        <v>3.679386264611777</v>
       </c>
       <c r="F7" t="n">
-        <v>6.557234113453891</v>
+        <v>9.342802250073984</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1207646532306125</v>
+        <v>0.04564301814238057</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4195043404282328</v>
+        <v>-0.7346025373375803</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7053761703161521</v>
+        <v>-0.8456967666532019</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6205745973369434</v>
+        <v>-0.865679069398071</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0003674761130354605</v>
+        <v>-0.08547188705583565</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.330807041441402</v>
+        <v>-0.4707695804958292</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.001177598819434855</v>
+        <v>-0.01589458051036038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>59.13244876376572</v>
+        <v>52.73522674138431</v>
       </c>
       <c r="B8" t="n">
-        <v>106.9213445487205</v>
+        <v>114.1879384954688</v>
       </c>
       <c r="C8" t="n">
-        <v>45.50168807183208</v>
+        <v>45.50299326496759</v>
       </c>
       <c r="D8" t="n">
-        <v>11.20729807397916</v>
+        <v>11.53683980371371</v>
       </c>
       <c r="E8" t="n">
-        <v>4.62586730380001</v>
+        <v>4.177610781464498</v>
       </c>
       <c r="F8" t="n">
-        <v>6.41416901986063</v>
+        <v>5.638616662798301</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1341104593123138</v>
+        <v>0.2064303588870738</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3705039276390916</v>
+        <v>-0.1172140941029831</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6856315929893331</v>
+        <v>-0.5897180142303349</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5774029700811418</v>
+        <v>-0.3375679106184631</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0505001068392279</v>
+        <v>-0.009427573561001103</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3184933657282429</v>
+        <v>-0.2705142005603823</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0003751270737967216</v>
+        <v>-0.00066516999279842</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89.06775830209052</v>
+        <v>52.1187478395636</v>
       </c>
       <c r="B9" t="n">
-        <v>84.04005808711139</v>
+        <v>115.7948092155232</v>
       </c>
       <c r="C9" t="n">
-        <v>45.57419476210057</v>
+        <v>45.50211308594167</v>
       </c>
       <c r="D9" t="n">
-        <v>9.581429440713494</v>
+        <v>11.53683980371371</v>
       </c>
       <c r="E9" t="n">
-        <v>4.615596425470478</v>
+        <v>4.271888626569369</v>
       </c>
       <c r="F9" t="n">
-        <v>11.31091938339543</v>
+        <v>5.56241845173659</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03082327965734244</v>
+        <v>0.2157997490178718</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8072696774718505</v>
+        <v>-0.08598054612067255</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8824562752136177</v>
+        <v>-0.5784697434660475</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9118563707605933</v>
+        <v>-0.3062279469969738</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1522015721474224</v>
+        <v>-0.0003064374560612274</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4762073685391111</v>
+        <v>-0.265890608796727</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01648772491123898</v>
+        <v>-0.0004695746537028422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69.36732491535558</v>
+        <v>83.34814438104752</v>
       </c>
       <c r="B10" t="n">
-        <v>91.00268089486647</v>
+        <v>79.34132778328878</v>
       </c>
       <c r="C10" t="n">
-        <v>45.64770125880625</v>
+        <v>45.5024332745697</v>
       </c>
       <c r="D10" t="n">
-        <v>10.1139602223757</v>
+        <v>9.16291206248223</v>
       </c>
       <c r="E10" t="n">
-        <v>4.531457072822088</v>
+        <v>3.917135476506693</v>
       </c>
       <c r="F10" t="n">
-        <v>7.746354335189359</v>
+        <v>10.06034584583473</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07420021259768191</v>
+        <v>0.03859789167382363</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6062193237169036</v>
+        <v>-0.7690145310032953</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7850695907909517</v>
+        <v>-0.8630873333501023</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7733530089114184</v>
+        <v>-0.8882431395050561</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03405116723854843</v>
+        <v>-0.04885449938940488</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3952549368651668</v>
+        <v>-0.4688555287149636</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03282250195694503</v>
+        <v>-0.0005407276821556284</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95.1696069098771</v>
+        <v>54.24516485981742</v>
       </c>
       <c r="B11" t="n">
-        <v>83.94340910127232</v>
+        <v>110.6919876685159</v>
       </c>
       <c r="C11" t="n">
-        <v>45.50117130475893</v>
+        <v>45.50258880377954</v>
       </c>
       <c r="D11" t="n">
-        <v>8.371759948029492</v>
+        <v>11.35547844556876</v>
       </c>
       <c r="E11" t="n">
-        <v>4.395637836782196</v>
+        <v>4.08462247048779</v>
       </c>
       <c r="F11" t="n">
-        <v>12.38448805488351</v>
+        <v>5.791762304854963</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02454954981289079</v>
+        <v>0.1853219388153006</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.840779479535534</v>
+        <v>-0.1880439483902884</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9009833959556249</v>
+        <v>-0.615683717445042</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9315595857554452</v>
+        <v>-0.4073055389388014</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0416367009838167</v>
+        <v>-0.000625879137433483</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5173948466416706</v>
+        <v>-0.2818387364486307</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0002602899464278219</v>
+        <v>-0.0005752897287866765</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67.2162856914923</v>
+        <v>95.20035697381508</v>
       </c>
       <c r="B12" t="n">
-        <v>107.6149119705437</v>
+        <v>70.09475400306819</v>
       </c>
       <c r="C12" t="n">
-        <v>45.51302571402948</v>
+        <v>45.52785833036355</v>
       </c>
       <c r="D12" t="n">
-        <v>11.20102560714735</v>
+        <v>8.32120473775643</v>
       </c>
       <c r="E12" t="n">
-        <v>4.269149524445451</v>
+        <v>3.890287444017305</v>
       </c>
       <c r="F12" t="n">
-        <v>7.616744140562708</v>
+        <v>12.38203236601479</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08376386413068145</v>
+        <v>0.02451883642994887</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5627975562119415</v>
+        <v>-0.8409352662272457</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7644181520257513</v>
+        <v>-0.9010747886442132</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7387894410944169</v>
+        <v>-0.9316489972567146</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0709855435564536</v>
+        <v>-0.03132331748720932</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3287099284175731</v>
+        <v>-0.5176024095732518</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.002894603117661876</v>
+        <v>-0.006190740080790069</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>86.71648806388619</v>
+        <v>88.06512634762433</v>
       </c>
       <c r="B13" t="n">
-        <v>79.45610219413592</v>
+        <v>70.52935869204822</v>
       </c>
       <c r="C13" t="n">
-        <v>45.64200538799279</v>
+        <v>45.50491545867708</v>
       </c>
       <c r="D13" t="n">
-        <v>9.532367238234256</v>
+        <v>8.705553015778261</v>
       </c>
       <c r="E13" t="n">
-        <v>4.468206364146207</v>
+        <v>3.107679345450464</v>
       </c>
       <c r="F13" t="n">
-        <v>10.81683954247323</v>
+        <v>10.91934823591961</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0337573295364915</v>
+        <v>0.03189940367840726</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7918929889910705</v>
+        <v>-0.8028673701415285</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8742576276141885</v>
+        <v>-0.8808201468058712</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9024319547370905</v>
+        <v>-0.9093908496124233</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.09926650020990135</v>
+        <v>-0.06227042687653939</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4603362944312317</v>
+        <v>-0.4773949460950266</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.03155675288728579</v>
+        <v>-0.001092324150461232</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66.42094955069625</v>
+        <v>61.55554279229021</v>
       </c>
       <c r="B14" t="n">
-        <v>95.23963491442517</v>
+        <v>102.6348460253017</v>
       </c>
       <c r="C14" t="n">
-        <v>46.75791389288461</v>
+        <v>45.50431524988107</v>
       </c>
       <c r="D14" t="n">
-        <v>10.12719599323144</v>
+        <v>10.70197706702258</v>
       </c>
       <c r="E14" t="n">
-        <v>4.708606403618543</v>
+        <v>3.080236236198851</v>
       </c>
       <c r="F14" t="n">
-        <v>7.32833124354959</v>
+        <v>6.655348043545253</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08697378705131817</v>
+        <v>0.1151439007570892</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5528455767349193</v>
+        <v>-0.4409326810285629</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7614250272698512</v>
+        <v>-0.7141322930051179</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7317018869770359</v>
+        <v>-0.6390680612361973</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.004373622212360259</v>
+        <v>-0.0005570921107652741</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3731571216302219</v>
+        <v>-0.3366665709421766</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2795364206410251</v>
+        <v>-0.0009589444180153894</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>56.42042273107171</v>
+        <v>57.90478382174796</v>
       </c>
       <c r="B15" t="n">
-        <v>113.3845583176879</v>
+        <v>110.111966032564</v>
       </c>
       <c r="C15" t="n">
-        <v>45.50165914329433</v>
+        <v>45.50867190811474</v>
       </c>
       <c r="D15" t="n">
-        <v>11.47233343440334</v>
+        <v>11.61889966531507</v>
       </c>
       <c r="E15" t="n">
-        <v>4.936676842556344</v>
+        <v>4.435197522265234</v>
       </c>
       <c r="F15" t="n">
-        <v>6.099240592778676</v>
+        <v>6.329540756479473</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1600871442428268</v>
+        <v>0.1454773300651366</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2768984331055121</v>
+        <v>-0.3300714098605856</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6491053341457362</v>
+        <v>-0.6696376164453818</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4918960278781689</v>
+        <v>-0.5409111985431938</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01116276098371173</v>
+        <v>-0.05654948038924245</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2769955119588859</v>
+        <v>-0.2875715847299541</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0003686985098498574</v>
+        <v>-0.001927090692163402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>72.79981081695044</v>
+        <v>70.29535880325403</v>
       </c>
       <c r="B16" t="n">
-        <v>87.98383020412624</v>
+        <v>96.09302181434427</v>
       </c>
       <c r="C16" t="n">
-        <v>45.55935791651491</v>
+        <v>45.54926548864899</v>
       </c>
       <c r="D16" t="n">
-        <v>9.663940998877413</v>
+        <v>10.23827648329205</v>
       </c>
       <c r="E16" t="n">
-        <v>4.421364173916073</v>
+        <v>4.679842963607094</v>
       </c>
       <c r="F16" t="n">
-        <v>8.224967713576492</v>
+        <v>7.920050750948153</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06221862665873853</v>
+        <v>0.07078510174307198</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6580713477518474</v>
+        <v>-0.6211615374469707</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8088616921054773</v>
+        <v>-0.7918173693550146</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8120735034385707</v>
+        <v>-0.7846835801088705</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01212052307480621</v>
+        <v>-0.006958401255735856</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4209985811271283</v>
+        <v>-0.3758544314731851</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.01319064811442616</v>
+        <v>-0.01094788636644306</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92.88344082388954</v>
+        <v>92.45385427726335</v>
       </c>
       <c r="B17" t="n">
-        <v>104.6418309875705</v>
+        <v>88.10723612940765</v>
       </c>
       <c r="C17" t="n">
-        <v>45.5006965082443</v>
+        <v>45.50090193688065</v>
       </c>
       <c r="D17" t="n">
-        <v>8.566006109653447</v>
+        <v>8.940212294780371</v>
       </c>
       <c r="E17" t="n">
-        <v>4.241719871493617</v>
+        <v>3.732095519370459</v>
       </c>
       <c r="F17" t="n">
-        <v>11.91775452155533</v>
+        <v>11.90058444763233</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0266417898034612</v>
+        <v>0.02710090462735949</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8293090440379364</v>
+        <v>-0.8269474533658396</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8945771107527304</v>
+        <v>-0.8932386148343974</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9249616277483732</v>
+        <v>-0.9235769066749246</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0296590342409438</v>
+        <v>-0.09957932910805176</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5019632255612545</v>
+        <v>-0.4990635163715276</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0001547796098436138</v>
+        <v>-0.0002004304179215044</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96.79084611570778</v>
+        <v>85.74317657459946</v>
       </c>
       <c r="B18" t="n">
-        <v>98.67745587538779</v>
+        <v>69.90994144456067</v>
       </c>
       <c r="C18" t="n">
-        <v>45.50080363780708</v>
+        <v>45.50043142300733</v>
       </c>
       <c r="D18" t="n">
-        <v>8.024716748945318</v>
+        <v>8.635165912068578</v>
       </c>
       <c r="E18" t="n">
-        <v>4.62762308001257</v>
+        <v>4.721399518987327</v>
       </c>
       <c r="F18" t="n">
-        <v>12.68005598878772</v>
+        <v>10.42931108399751</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02318397533099648</v>
+        <v>0.03492725735615525</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8483144495101032</v>
+        <v>-0.787167935541407</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9052635982065668</v>
+        <v>-0.8725295800610335</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9358141510861017</v>
+        <v>-0.8997249587437793</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.001416756773843922</v>
+        <v>-0.1014688219083875</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5283382112810275</v>
+        <v>-0.3797325446280228</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.000178586179351431</v>
+        <v>-9.587177940778568e-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>61.9006506826487</v>
+        <v>55.11756306532092</v>
       </c>
       <c r="B19" t="n">
-        <v>117.5413617530147</v>
+        <v>111.3362224680047</v>
       </c>
       <c r="C19" t="n">
-        <v>45.86139658957606</v>
+        <v>46.58591228440859</v>
       </c>
       <c r="D19" t="n">
-        <v>11.46676609054558</v>
+        <v>11.20200565333868</v>
       </c>
       <c r="E19" t="n">
-        <v>4.555169654633656</v>
+        <v>4.724813607976846</v>
       </c>
       <c r="F19" t="n">
-        <v>6.880572669583159</v>
+        <v>5.927345966048753</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1135397576715953</v>
+        <v>0.1747177847954558</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4428540240042511</v>
+        <v>-0.2252994831339694</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7133019029560835</v>
+        <v>-0.6295546607637187</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6395231917634642</v>
+        <v>-0.4431553604357706</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.04917437886169593</v>
+        <v>-0.01006433641554422</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2928293921078787</v>
+        <v>-0.2883817229899068</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.08031035323912444</v>
+        <v>-0.2413138409796878</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>58.49251092598757</v>
+        <v>71.64797081710132</v>
       </c>
       <c r="B20" t="n">
-        <v>105.8081663914527</v>
+        <v>91.2444031110447</v>
       </c>
       <c r="C20" t="n">
-        <v>45.50716508247302</v>
+        <v>45.50227130907457</v>
       </c>
       <c r="D20" t="n">
-        <v>10.98764596996613</v>
+        <v>10.34958908943175</v>
       </c>
       <c r="E20" t="n">
-        <v>4.89998674582955</v>
+        <v>4.114041478254876</v>
       </c>
       <c r="F20" t="n">
-        <v>6.280785874385895</v>
+        <v>8.166865917904211</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1393946286206823</v>
+        <v>0.06615193384310021</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3501726438864315</v>
+        <v>-0.6416039800582802</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6776212488035572</v>
+        <v>-0.8011663140474834</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5592045228579505</v>
+        <v>-0.799949945250474</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.001977350285914553</v>
+        <v>-0.05068455467473532</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3136938319449067</v>
+        <v>-0.3854917920718469</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.001592240549561086</v>
+        <v>-0.0005047353499042229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>55.81552311702157</v>
+        <v>72.97045794549159</v>
       </c>
       <c r="B21" t="n">
-        <v>113.3845583176879</v>
+        <v>88.61484473659154</v>
       </c>
       <c r="C21" t="n">
-        <v>46.13964842603571</v>
+        <v>45.50164840839488</v>
       </c>
       <c r="D21" t="n">
-        <v>11.41532938865353</v>
+        <v>9.672059395464014</v>
       </c>
       <c r="E21" t="n">
-        <v>4.559062871197797</v>
+        <v>4.720604768246668</v>
       </c>
       <c r="F21" t="n">
-        <v>6.04035868301346</v>
+        <v>8.253425855968144</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1668198292177838</v>
+        <v>0.06170033712312306</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2534462924876508</v>
+        <v>-0.660394041261211</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6401550764818051</v>
+        <v>-0.8099464861670155</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4698636736070311</v>
+        <v>-0.8137641820299907</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.006381295124147905</v>
+        <v>-0.0161098541289893</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2726856022087787</v>
+        <v>-0.4222784345911869</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1421440946746025</v>
+        <v>-0.0003663129766388884</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>52.44004466385624</v>
+        <v>69.43765844131936</v>
       </c>
       <c r="B22" t="n">
-        <v>113.2970272098338</v>
+        <v>91.04725554215474</v>
       </c>
       <c r="C22" t="n">
-        <v>45.50048898919626</v>
+        <v>45.53092594788551</v>
       </c>
       <c r="D22" t="n">
-        <v>11.51357193935704</v>
+        <v>9.958499050193108</v>
       </c>
       <c r="E22" t="n">
-        <v>4.90628390315099</v>
+        <v>3.191632721118912</v>
       </c>
       <c r="F22" t="n">
-        <v>5.597147468557528</v>
+        <v>7.720688595217656</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2108049063927787</v>
+        <v>0.07383889026907112</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1024681440817736</v>
+        <v>-0.6074492418377063</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5843985449636837</v>
+        <v>-0.7856408886685941</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3228220872904567</v>
+        <v>-0.7743013199110833</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.001001656492445944</v>
+        <v>-0.00259000110562748</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2683003349789218</v>
+        <v>-0.3957824383098952</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0001086642658360004</v>
+        <v>-0.006872432863447159</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>78.95444917463072</v>
+        <v>51.46413075315019</v>
       </c>
       <c r="B23" t="n">
-        <v>77.79119521600335</v>
+        <v>115.7588024245097</v>
       </c>
       <c r="C23" t="n">
-        <v>45.50023397103432</v>
+        <v>45.50100615303876</v>
       </c>
       <c r="D23" t="n">
-        <v>9.667476738170564</v>
+        <v>11.60296685059961</v>
       </c>
       <c r="E23" t="n">
-        <v>4.876545429297965</v>
+        <v>3.932101401136856</v>
       </c>
       <c r="F23" t="n">
-        <v>9.323454590089273</v>
+        <v>5.496017412859053</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04671373166372051</v>
+        <v>0.2264958744454725</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7298226280422307</v>
+        <v>-0.0510813819142571</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8433044364117959</v>
+        <v>-0.5660147282629119</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8624566003744881</v>
+        <v>-0.2707715035482616</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1405718829132293</v>
+        <v>-0.002054713025941408</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4671583688097305</v>
+        <v>-0.2609809806486265</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.199356318291715e-05</v>
+        <v>-0.0002235895641686247</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>54.14669860888688</v>
+        <v>81.6434316350127</v>
       </c>
       <c r="B24" t="n">
-        <v>113.2970272098338</v>
+        <v>83.14472853206115</v>
       </c>
       <c r="C24" t="n">
-        <v>45.50072110993689</v>
+        <v>45.50050728920269</v>
       </c>
       <c r="D24" t="n">
-        <v>11.4889067150443</v>
+        <v>9.284322253933775</v>
       </c>
       <c r="E24" t="n">
-        <v>4.528026145427287</v>
+        <v>4.955265898090509</v>
       </c>
       <c r="F24" t="n">
-        <v>5.806412975782543</v>
+        <v>9.753769994053396</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1868061118812253</v>
+        <v>0.04148307277700133</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1835438391456258</v>
+        <v>-0.7548135299817662</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6139933584600316</v>
+        <v>-0.8558368697929636</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4029097009597755</v>
+        <v>-0.8790553556969453</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.02213236639850854</v>
+        <v>-0.0366900212757497</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2811002395666515</v>
+        <v>-0.4567094503994654</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0001602466526423596</v>
+        <v>-0.0001127309339325755</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>53.30103771707734</v>
+        <v>91.72460326145379</v>
       </c>
       <c r="B25" t="n">
-        <v>114.5980056035124</v>
+        <v>63.96847965087868</v>
       </c>
       <c r="C25" t="n">
-        <v>45.50826840660252</v>
+        <v>45.50056505531358</v>
       </c>
       <c r="D25" t="n">
-        <v>11.48079377816278</v>
+        <v>7.679634146865924</v>
       </c>
       <c r="E25" t="n">
-        <v>4.473619715759381</v>
+        <v>3.632421364835821</v>
       </c>
       <c r="F25" t="n">
-        <v>5.698094707260344</v>
+        <v>11.48423133072977</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1981953850872386</v>
+        <v>0.02768052748343083</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1446837207267811</v>
+        <v>-0.8246374320257439</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5997139743002311</v>
+        <v>-0.892617878740538</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3648407150089796</v>
+        <v>-0.9223914466747345</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.008309735163975497</v>
+        <v>-0.06272935886986565</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2747577828780801</v>
+        <v>-0.1271834178497293</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.001837423689449724</v>
+        <v>-0.000125567847461816</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51.11145952460996</v>
+        <v>74.54673708091482</v>
       </c>
       <c r="B26" t="n">
-        <v>117.2172557998355</v>
+        <v>85.12314961749699</v>
       </c>
       <c r="C26" t="n">
-        <v>45.50210609590636</v>
+        <v>45.50489747586949</v>
       </c>
       <c r="D26" t="n">
-        <v>11.63768137852997</v>
+        <v>9.520554124356224</v>
       </c>
       <c r="E26" t="n">
-        <v>4.231230210288467</v>
+        <v>3.091782900138467</v>
       </c>
       <c r="F26" t="n">
-        <v>5.460564764052077</v>
+        <v>8.496484148131826</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2325422106327668</v>
+        <v>0.05713598984574899</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.03153309309832881</v>
+        <v>-0.68089446080465</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5590947790431544</v>
+        <v>-0.8196133018006887</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2507199601846328</v>
+        <v>-0.8285234382041635</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.002887154167262805</v>
+        <v>-0.01875501879250919</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2583359464345747</v>
+        <v>-0.4341005281068612</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0004680213125236865</v>
+        <v>-0.001088327970998892</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>77.87461437709104</v>
+        <v>63.58393913054022</v>
       </c>
       <c r="B27" t="n">
-        <v>87.88598374094622</v>
+        <v>98.92223283779727</v>
       </c>
       <c r="C27" t="n">
-        <v>45.50208988329149</v>
+        <v>45.50030548408045</v>
       </c>
       <c r="D27" t="n">
-        <v>9.639638860387576</v>
+        <v>10.66550430789028</v>
       </c>
       <c r="E27" t="n">
-        <v>4.577412363672374</v>
+        <v>2.833230424619265</v>
       </c>
       <c r="F27" t="n">
-        <v>9.11832510581019</v>
+        <v>6.946726420051331</v>
       </c>
       <c r="G27" t="n">
-        <v>0.04901541068358189</v>
+        <v>0.1021844724604208</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7188395853442953</v>
+        <v>-0.4917064071649396</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8378989599788451</v>
+        <v>-0.7352316204628053</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8550021984118833</v>
+        <v>-0.6819320573615812</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.03080882412261113</v>
+        <v>-0.02863066633462032</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4298566274367736</v>
+        <v>-0.3518795434790516</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0004644185092195219</v>
+        <v>-6.788535121066142e-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>76.75346085259704</v>
+        <v>75.38571569573189</v>
       </c>
       <c r="B28" t="n">
-        <v>82.58359686408994</v>
+        <v>81.69211004498399</v>
       </c>
       <c r="C28" t="n">
-        <v>45.57805404976377</v>
+        <v>45.50481753006137</v>
       </c>
       <c r="D28" t="n">
-        <v>9.478467598455374</v>
+        <v>9.495481829111444</v>
       </c>
       <c r="E28" t="n">
-        <v>4.880795510498761</v>
+        <v>4.034486792180761</v>
       </c>
       <c r="F28" t="n">
-        <v>8.884326809138209</v>
+        <v>8.639539622717729</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05153449416580679</v>
+        <v>0.0549090865998198</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.706806197380668</v>
+        <v>-0.6911054943115392</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8320445575241012</v>
+        <v>-0.824481898594538</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.8467280907117487</v>
+        <v>-0.8357582676672137</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.05964550202509194</v>
+        <v>-0.03180150218723343</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.4506509563944778</v>
+        <v>-0.4403928677179891</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.01734534439194885</v>
+        <v>-0.001070562235861994</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>54.89406667713854</v>
+        <v>62.4940104283875</v>
       </c>
       <c r="B29" t="n">
-        <v>111.7686552574002</v>
+        <v>102.3678995770405</v>
       </c>
       <c r="C29" t="n">
-        <v>45.50143656472753</v>
+        <v>45.67758271607475</v>
       </c>
       <c r="D29" t="n">
-        <v>11.29912420101287</v>
+        <v>10.70197706702258</v>
       </c>
       <c r="E29" t="n">
-        <v>4.96594794460164</v>
+        <v>2.918620990687768</v>
       </c>
       <c r="F29" t="n">
-        <v>5.863598137539924</v>
+        <v>6.800842360864193</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1771439279427025</v>
+        <v>0.1089423483613153</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2161112836433118</v>
+        <v>-0.4652075548090822</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6261420313707826</v>
+        <v>-0.7241452138425569</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4343910715893854</v>
+        <v>-0.6597240502313142</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0006207231999994493</v>
+        <v>-0.02032424839442667</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.286705500078539</v>
+        <v>-0.3437050782129063</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0003192366061174901</v>
+        <v>-0.03946282579439034</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>61.29264342623921</v>
+        <v>93.1905451401351</v>
       </c>
       <c r="B30" t="n">
-        <v>114.0958313789569</v>
+        <v>76.58454475205876</v>
       </c>
       <c r="C30" t="n">
-        <v>45.50080688601455</v>
+        <v>43.12568325064041</v>
       </c>
       <c r="D30" t="n">
-        <v>11.46676609054558</v>
+        <v>8.940212294780371</v>
       </c>
       <c r="E30" t="n">
-        <v>4.768187731948793</v>
+        <v>4.394334122250475</v>
       </c>
       <c r="F30" t="n">
-        <v>6.773723748713812</v>
+        <v>12.1396454375208</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1176692785875032</v>
+        <v>0.0264317552052842</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4265466666369437</v>
+        <v>-0.8307383867072579</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7066254288943665</v>
+        <v>-0.8952988107620966</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6254568029749692</v>
+        <v>-0.9257746942911047</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.03355700319313879</v>
+        <v>-0.06719077797462596</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.2887253431271147</v>
+        <v>-0.5040361796959121</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0001793080032340411</v>
+        <v>-0.2808742121477756</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>57.50328551157219</v>
+        <v>56.22745400555595</v>
       </c>
       <c r="B31" t="n">
-        <v>106.9213445487205</v>
+        <v>110.8057468180228</v>
       </c>
       <c r="C31" t="n">
-        <v>45.50168807183208</v>
+        <v>45.51115373663303</v>
       </c>
       <c r="D31" t="n">
-        <v>11.20857889866618</v>
+        <v>11.36006657614722</v>
       </c>
       <c r="E31" t="n">
-        <v>4.624075052795638</v>
+        <v>4.271709718744782</v>
       </c>
       <c r="F31" t="n">
-        <v>6.190570827801788</v>
+        <v>6.051129572670567</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1487955389129773</v>
+        <v>0.1620021128431705</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.316518187266698</v>
+        <v>-0.2696489374879388</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6644222841818915</v>
+        <v>-0.646354229638001</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5285889730485721</v>
+        <v>-0.485133143276764</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.02525213510334171</v>
+        <v>-0.03178482360875007</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.3062746413367914</v>
+        <v>-0.2967059050416696</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0003751270737967216</v>
+        <v>-0.002478608140675798</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>82.49528361819831</v>
+        <v>80.75067696023095</v>
       </c>
       <c r="B32" t="n">
-        <v>91.82659557202913</v>
+        <v>78.97045668409461</v>
       </c>
       <c r="C32" t="n">
-        <v>45.50135050985726</v>
+        <v>45.50100172852172</v>
       </c>
       <c r="D32" t="n">
-        <v>9.530100114147602</v>
+        <v>9.300629497907384</v>
       </c>
       <c r="E32" t="n">
-        <v>4.0470774086999</v>
+        <v>4.516291969084649</v>
       </c>
       <c r="F32" t="n">
-        <v>9.968853517429876</v>
+        <v>9.586331333424885</v>
       </c>
       <c r="G32" t="n">
-        <v>0.04007050926330172</v>
+        <v>0.04310097431546687</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7597322890600157</v>
+        <v>-0.7469032115878192</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.85755011438842</v>
+        <v>-0.8518448479492872</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8819847163097383</v>
+        <v>-0.8738615410702394</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.01414801866759661</v>
+        <v>-0.02086793231578518</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.4318431644228387</v>
+        <v>-0.4503485733416455</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0003001133016151958</v>
+        <v>-0.0002226063381603749</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>51.78390099859977</v>
+        <v>96.37729345897972</v>
       </c>
       <c r="B33" t="n">
-        <v>117.5384012575644</v>
+        <v>83.75028351837065</v>
       </c>
       <c r="C33" t="n">
-        <v>45.50024231235829</v>
+        <v>45.50056322938575</v>
       </c>
       <c r="D33" t="n">
-        <v>11.61223926451446</v>
+        <v>9.258923502609502</v>
       </c>
       <c r="E33" t="n">
-        <v>4.876321052969057</v>
+        <v>4.213784739975689</v>
       </c>
       <c r="F33" t="n">
-        <v>5.536771711527805</v>
+        <v>12.83864173741224</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2212688464797467</v>
+        <v>0.02362497240522211</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.06830120381482659</v>
+        <v>-0.8462160213124301</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5721353609467722</v>
+        <v>-0.9039724961405363</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2883116530220571</v>
+        <v>-0.9346153228252937</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.008287560836624202</v>
+        <v>-0.2409878215938657</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.2633792574894983</v>
+        <v>-0.5255467308481132</v>
       </c>
       <c r="M33" t="n">
-        <v>-5.384719073159294e-05</v>
+        <v>-0.0001251620857224689</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>90.85018828667128</v>
+        <v>53.51447872274482</v>
       </c>
       <c r="B34" t="n">
-        <v>85.31841181308857</v>
+        <v>113.6674251007953</v>
       </c>
       <c r="C34" t="n">
-        <v>45.50074003021965</v>
+        <v>45.93230058084708</v>
       </c>
       <c r="D34" t="n">
-        <v>8.976313163800858</v>
+        <v>11.38497754238666</v>
       </c>
       <c r="E34" t="n">
-        <v>4.562703160892216</v>
+        <v>4.57829244254409</v>
       </c>
       <c r="F34" t="n">
-        <v>11.56165805640738</v>
+        <v>5.727056170110471</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02874653663899845</v>
+        <v>0.1952522990611615</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8180622515445731</v>
+        <v>-0.1547144856153557</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8883646086450266</v>
+        <v>-0.6033804906334728</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9183432884025647</v>
+        <v>-0.3747215179759982</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.07173166606106487</v>
+        <v>-0.003995663209209598</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.4882387709350311</v>
+        <v>-0.2763585904205861</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0001644511599209475</v>
+        <v>-0.09606679574379731</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>84.66256219788217</v>
+        <v>54.98612949591345</v>
       </c>
       <c r="B35" t="n">
-        <v>91.82659557202913</v>
+        <v>110.7708535490749</v>
       </c>
       <c r="C35" t="n">
-        <v>45.50135050985726</v>
+        <v>45.5086409451662</v>
       </c>
       <c r="D35" t="n">
-        <v>9.530100114147602</v>
+        <v>11.30080301060471</v>
       </c>
       <c r="E35" t="n">
-        <v>4.0470774086999</v>
+        <v>4.244560675326797</v>
       </c>
       <c r="F35" t="n">
-        <v>10.3956517819371</v>
+        <v>5.876225744486804</v>
       </c>
       <c r="G35" t="n">
-        <v>0.03664205658979677</v>
+        <v>0.176039238388816</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7770429830092112</v>
+        <v>-0.2199759505368103</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8664739012582432</v>
+        <v>-0.6275880984618183</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.893110952314547</v>
+        <v>-0.4380936035315646</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.05621670264653518</v>
+        <v>-0.002488915577752424</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.4464722948357046</v>
+        <v>-0.2873959712193509</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0003001133016151958</v>
+        <v>-0.001920210036933656</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>73.3784255779765</v>
+        <v>68.02173878265893</v>
       </c>
       <c r="B36" t="n">
-        <v>114.2679019249899</v>
+        <v>96.09302181434427</v>
       </c>
       <c r="C36" t="n">
-        <v>45.77549425248953</v>
+        <v>45.54926548864899</v>
       </c>
       <c r="D36" t="n">
-        <v>10.48285704378506</v>
+        <v>10.45052510872786</v>
       </c>
       <c r="E36" t="n">
-        <v>4.268128238164211</v>
+        <v>4.679842963607094</v>
       </c>
       <c r="F36" t="n">
-        <v>8.502699791333249</v>
+        <v>7.593067074488051</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0608224514930789</v>
+        <v>0.07980949788133659</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.662001584346402</v>
+        <v>-0.5829068873182742</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8095945651643175</v>
+        <v>-0.7746255600778947</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8144068930177538</v>
+        <v>-0.7553644721578963</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.0441479014194763</v>
+        <v>-0.008038127475152172</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.3703043726513414</v>
+        <v>-0.3596548888264448</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.06122094499767292</v>
+        <v>-0.01094788636644306</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>52.76859438663975</v>
+        <v>89.96846797159577</v>
       </c>
       <c r="B37" t="n">
-        <v>113.2970272098338</v>
+        <v>78.57843287846109</v>
       </c>
       <c r="C37" t="n">
-        <v>45.5007054215331</v>
+        <v>45.50047751168648</v>
       </c>
       <c r="D37" t="n">
-        <v>11.51357193935704</v>
+        <v>8.912926289882172</v>
       </c>
       <c r="E37" t="n">
-        <v>4.248701446765338</v>
+        <v>3.71373083396856</v>
       </c>
       <c r="F37" t="n">
-        <v>5.637881108660547</v>
+        <v>11.36084306335365</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2058951327670165</v>
+        <v>0.02969951465528593</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1188893025130705</v>
+        <v>-0.8129283112506465</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5903291423488756</v>
+        <v>-0.8855814123142324</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3392437722006886</v>
+        <v>-0.9152828628743656</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.00587694729770174</v>
+        <v>-0.03895066384016962</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.2707644578997981</v>
+        <v>-0.4822871588082714</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0001567603406880946</v>
+        <v>-0.0001061137081055652</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>55.17421669732963</v>
+        <v>85.42279968910393</v>
       </c>
       <c r="B38" t="n">
-        <v>113.3289551294293</v>
+        <v>69.90994144456067</v>
       </c>
       <c r="C38" t="n">
-        <v>45.50048698624079</v>
+        <v>45.50039408361892</v>
       </c>
       <c r="D38" t="n">
-        <v>11.51357193935704</v>
+        <v>8.576228834601469</v>
       </c>
       <c r="E38" t="n">
-        <v>4.90628390315099</v>
+        <v>4.721399518987327</v>
       </c>
       <c r="F38" t="n">
-        <v>5.943785872477035</v>
+        <v>10.352638110074</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1741115873789819</v>
+        <v>0.03536692911571862</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2276042328828019</v>
+        <v>-0.784874651216018</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6304122420289784</v>
+        <v>-0.871333208250146</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4453482638333464</v>
+        <v>-0.8982937600770998</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.000637828827231058</v>
+        <v>-0.08057806862336842</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.2681162939684736</v>
+        <v>-0.393259568682279</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0001082191646178954</v>
+        <v>-8.757413753737731e-05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>85.65141418165091</v>
+        <v>57.04410131676654</v>
       </c>
       <c r="B39" t="n">
-        <v>84.12938577393257</v>
+        <v>113.5116080828412</v>
       </c>
       <c r="C39" t="n">
-        <v>45.50471788396048</v>
+        <v>46.02529634946956</v>
       </c>
       <c r="D39" t="n">
-        <v>9.639638860387576</v>
+        <v>11.36122116905129</v>
       </c>
       <c r="E39" t="n">
-        <v>4.563451380295612</v>
+        <v>4.680975881704796</v>
       </c>
       <c r="F39" t="n">
-        <v>10.61663619390126</v>
+        <v>6.186629253953937</v>
       </c>
       <c r="G39" t="n">
-        <v>0.03522926637151121</v>
+        <v>0.1536708163601935</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.784337987411865</v>
+        <v>-0.2999459352109247</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8702708884574817</v>
+        <v>-0.6579588666527618</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8977128093946055</v>
+        <v>-0.5132993725419406</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.09632399921605396</v>
+        <v>-0.01202947416652915</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.4531470457261436</v>
+        <v>-0.2814392218819617</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.001048418657884354</v>
+        <v>-0.1167325221043466</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>70.59217209984514</v>
+        <v>51.19205344275227</v>
       </c>
       <c r="B40" t="n">
-        <v>90.63086827341395</v>
+        <v>117.7179072310698</v>
       </c>
       <c r="C40" t="n">
-        <v>45.7863895686375</v>
+        <v>45.50016884577438</v>
       </c>
       <c r="D40" t="n">
-        <v>10.48285704378506</v>
+        <v>11.63357466900446</v>
       </c>
       <c r="E40" t="n">
-        <v>4.540300317131257</v>
+        <v>4.537483554780665</v>
       </c>
       <c r="F40" t="n">
-        <v>8.030633500254366</v>
+        <v>5.469335919236009</v>
       </c>
       <c r="G40" t="n">
-        <v>0.06986052162592594</v>
+        <v>0.2311493264700155</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6256858394716295</v>
+        <v>-0.03604372290814719</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7938492813996564</v>
+        <v>-0.560687269516132</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.788072528745508</v>
+        <v>-0.2553579035191613</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1250985856352963</v>
+        <v>-0.003313758710658526</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.4044412907488386</v>
+        <v>-0.2589404008206421</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.06364212636388838</v>
+        <v>-3.752128319420289e-05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>80.4842965215981</v>
+        <v>56.99940180342155</v>
       </c>
       <c r="B41" t="n">
-        <v>84.23623158190821</v>
+        <v>113.56795846218</v>
       </c>
       <c r="C41" t="n">
-        <v>45.50095274129649</v>
+        <v>45.56407776640644</v>
       </c>
       <c r="D41" t="n">
-        <v>9.476748122230983</v>
+        <v>11.36122116905129</v>
       </c>
       <c r="E41" t="n">
-        <v>4.8956318194379</v>
+        <v>4.680975881704796</v>
       </c>
       <c r="F41" t="n">
-        <v>9.571791234913324</v>
+        <v>6.157043651998531</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04364133945330787</v>
+        <v>0.1539743728936669</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7444426813585502</v>
+        <v>-0.2984200292571834</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8505987290305289</v>
+        <v>-0.6573888209574247</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8722310368315259</v>
+        <v>-0.5119064419840418</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.05132766298310198</v>
+        <v>-0.001508577228979776</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4484506127163864</v>
+        <v>-0.2811207378493785</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0002117202881078695</v>
+        <v>-0.01423950364587631</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>75.40387383632086</v>
+        <v>65.64219109806915</v>
       </c>
       <c r="B42" t="n">
-        <v>82.63971569408567</v>
+        <v>98.18595183132415</v>
       </c>
       <c r="C42" t="n">
-        <v>46.54885197651311</v>
+        <v>45.50551720625609</v>
       </c>
       <c r="D42" t="n">
-        <v>9.671110128595506</v>
+        <v>10.49423606911376</v>
       </c>
       <c r="E42" t="n">
-        <v>4.229185867669031</v>
+        <v>4.429850702685082</v>
       </c>
       <c r="F42" t="n">
-        <v>8.724165398210019</v>
+        <v>7.225255362209841</v>
       </c>
       <c r="G42" t="n">
-        <v>0.05499509865695688</v>
+        <v>0.09084429299291895</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.6912194222367427</v>
+        <v>-0.5370971996633703</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.8245061456087781</v>
+        <v>-0.754590275301669</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8358249756361038</v>
+        <v>-0.7190838914349765</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.08767946299665431</v>
+        <v>-0.0335219410873064</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.4405290537724065</v>
+        <v>-0.3673164332355185</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.2330782170029125</v>
+        <v>-0.001226045834687717</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>51.59971212284464</v>
+        <v>53.56953367721746</v>
       </c>
       <c r="B43" t="n">
-        <v>117.4323445982566</v>
+        <v>113.6760040724515</v>
       </c>
       <c r="C43" t="n">
-        <v>45.50023723167626</v>
+        <v>45.93230058084708</v>
       </c>
       <c r="D43" t="n">
-        <v>11.61307814645985</v>
+        <v>11.36126108923525</v>
       </c>
       <c r="E43" t="n">
-        <v>4.899899320062934</v>
+        <v>4.581738535373398</v>
       </c>
       <c r="F43" t="n">
-        <v>5.514509748943858</v>
+        <v>5.729099568166093</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2242724788065324</v>
+        <v>0.1944573435828849</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.05842731550421065</v>
+        <v>-0.1573034239469816</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5686206479036072</v>
+        <v>-0.6043338476079891</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.278265632664449</v>
+        <v>-0.3772708631132737</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.005745919853149289</v>
+        <v>-0.0006756556496686697</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.2619978409213348</v>
+        <v>-0.276771502579131</v>
       </c>
       <c r="M43" t="n">
-        <v>-5.271815027935167e-05</v>
+        <v>-0.09606679574379731</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>70.52317809059181</v>
+        <v>96.8557612064035</v>
       </c>
       <c r="B44" t="n">
-        <v>90.62211075281171</v>
+        <v>80.30748290555751</v>
       </c>
       <c r="C44" t="n">
-        <v>45.6465249265625</v>
+        <v>45.5024332745697</v>
       </c>
       <c r="D44" t="n">
-        <v>10.48285704378506</v>
+        <v>9.16291206248223</v>
       </c>
       <c r="E44" t="n">
-        <v>4.531858224878984</v>
+        <v>3.917135476506693</v>
       </c>
       <c r="F44" t="n">
-        <v>8.01256559671836</v>
+        <v>12.92798216435744</v>
       </c>
       <c r="G44" t="n">
-        <v>0.07009141949239811</v>
+        <v>0.02323223529815165</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.6246278654757863</v>
+        <v>-0.8483848886028517</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.793369990802649</v>
+        <v>-0.9052099451957707</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.7872793206653881</v>
+        <v>-0.9358332470946185</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.1212190206814597</v>
+        <v>-0.2350977936380355</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.4039238356794386</v>
+        <v>-0.5287763881432237</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.03256109479166616</v>
+        <v>-0.0005407276821556284</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>74.5704697227735</v>
+        <v>66.26551436684881</v>
       </c>
       <c r="B45" t="n">
-        <v>81.99252360894992</v>
+        <v>94.70694952468915</v>
       </c>
       <c r="C45" t="n">
-        <v>47.16903648514165</v>
+        <v>45.50223265440898</v>
       </c>
       <c r="D45" t="n">
-        <v>9.671110128595506</v>
+        <v>10.34958908943175</v>
       </c>
       <c r="E45" t="n">
-        <v>4.045828235583905</v>
+        <v>4.276000433951668</v>
       </c>
       <c r="F45" t="n">
-        <v>8.60390635204155</v>
+        <v>7.2923468310314</v>
       </c>
       <c r="G45" t="n">
-        <v>0.05724957121035425</v>
+        <v>0.08768167415616115</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.6810534506155997</v>
+        <v>-0.5497945887850971</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8196490401012237</v>
+        <v>-0.7601042713368399</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8286183286876535</v>
+        <v>-0.729273847874615</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.08270932190532577</v>
+        <v>-0.01772852644659969</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.4342785229208012</v>
+        <v>-0.371991357751366</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.3708969966981452</v>
+        <v>-0.0004961454242188856</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>91.96489388134665</v>
+        <v>56.22745400555595</v>
       </c>
       <c r="B46" t="n">
-        <v>84.09058037046334</v>
+        <v>110.8057468180228</v>
       </c>
       <c r="C46" t="n">
-        <v>45.86995202841973</v>
+        <v>45.51115373663303</v>
       </c>
       <c r="D46" t="n">
-        <v>8.665771298525412</v>
+        <v>11.36006657614722</v>
       </c>
       <c r="E46" t="n">
-        <v>4.431128480774402</v>
+        <v>4.267520010599799</v>
       </c>
       <c r="F46" t="n">
-        <v>11.75254989672688</v>
+        <v>6.051129572670567</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02756328845617958</v>
+        <v>0.1620021128431705</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.8243547637152974</v>
+        <v>-0.2696489374879388</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8918310936960375</v>
+        <v>-0.646354229638001</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9220637643613719</v>
+        <v>-0.485133143276764</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.03803039070809235</v>
+        <v>-0.03178482360875007</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.4957630336990899</v>
+        <v>-0.2967059050416696</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.082211561871052</v>
+        <v>-0.002478608140675798</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>57.66585386175041</v>
+        <v>68.02173878265893</v>
       </c>
       <c r="B47" t="n">
-        <v>106.9213445487205</v>
+        <v>92.83787745878908</v>
       </c>
       <c r="C47" t="n">
-        <v>45.50168807183208</v>
+        <v>45.54926548864899</v>
       </c>
       <c r="D47" t="n">
-        <v>11.20857889866618</v>
+        <v>10.45052510872786</v>
       </c>
       <c r="E47" t="n">
-        <v>4.623847892390534</v>
+        <v>4.383501147363457</v>
       </c>
       <c r="F47" t="n">
-        <v>6.21262817402951</v>
+        <v>7.593067074488051</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1472386490590211</v>
+        <v>0.07980949788133659</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.3221801794793172</v>
+        <v>-0.5829068873182742</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6666245395784539</v>
+        <v>-0.7746255600778947</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.5337704786990846</v>
+        <v>-0.7553644721578963</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.0277933043019553</v>
+        <v>-0.06905379751975224</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.3074939039631281</v>
+        <v>-0.3851630408699419</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0003751270737967216</v>
+        <v>-0.01094788636644306</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>81.30461777242115</v>
+        <v>64.9739947579838</v>
       </c>
       <c r="B48" t="n">
-        <v>78.24202011931126</v>
+        <v>98.22096841012095</v>
       </c>
       <c r="C48" t="n">
-        <v>45.54485701109712</v>
+        <v>45.52551890745911</v>
       </c>
       <c r="D48" t="n">
-        <v>9.482756217046269</v>
+        <v>10.38446322686347</v>
       </c>
       <c r="E48" t="n">
-        <v>4.566636444505114</v>
+        <v>4.494067395591813</v>
       </c>
       <c r="F48" t="n">
-        <v>9.731250671031118</v>
+        <v>7.100890232131915</v>
       </c>
       <c r="G48" t="n">
-        <v>0.04213303247821768</v>
+        <v>0.09422405878857193</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.751815679364694</v>
+        <v>-0.5230655159357261</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.8543083428266988</v>
+        <v>-0.748573021243336</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.8770889872747404</v>
+        <v>-0.7077347047032689</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.0703889933252401</v>
+        <v>-0.001314351126278603</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.4542954016285008</v>
+        <v>-0.3623049606848785</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.009968224688249316</v>
+        <v>-0.005670868324244849</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>98.36548523194527</v>
+        <v>63.12281620808553</v>
       </c>
       <c r="B49" t="n">
-        <v>112.9465896820662</v>
+        <v>98.92223283779727</v>
       </c>
       <c r="C49" t="n">
-        <v>45.50116320627902</v>
+        <v>45.50030548408045</v>
       </c>
       <c r="D49" t="n">
-        <v>7.868860486901653</v>
+        <v>10.66550430789028</v>
       </c>
       <c r="E49" t="n">
-        <v>4.772078561928847</v>
+        <v>2.833230424619265</v>
       </c>
       <c r="F49" t="n">
-        <v>13.01018680556619</v>
+        <v>6.877893273659403</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02197238018460881</v>
+        <v>0.1049479795592844</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8551331821037191</v>
+        <v>-0.4807359273053152</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9091616967948465</v>
+        <v>-0.7306277373437436</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9396018542417796</v>
+        <v>-0.6727862921887167</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.006300814294502767</v>
+        <v>-0.02067666916320697</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.5389670253156307</v>
+        <v>-0.3484211215606414</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0002584902842268921</v>
+        <v>-6.788535121066142e-05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>98.36548523194527</v>
+        <v>50.83579338906296</v>
       </c>
       <c r="B50" t="n">
-        <v>86.22331698930579</v>
+        <v>116.1439798794335</v>
       </c>
       <c r="C50" t="n">
-        <v>45.50116320627902</v>
+        <v>46.10901632058511</v>
       </c>
       <c r="D50" t="n">
-        <v>7.868860486901653</v>
+        <v>11.63357466900446</v>
       </c>
       <c r="E50" t="n">
-        <v>4.769823339668307</v>
+        <v>4.508161714119675</v>
       </c>
       <c r="F50" t="n">
-        <v>13.01018680556619</v>
+        <v>5.458387741437021</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02197238018460881</v>
+        <v>0.2376800466356627</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8551331821037191</v>
+        <v>-0.01571858104855333</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9091616967948465</v>
+        <v>-0.5534988002226555</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9396018542417796</v>
+        <v>-0.2343673283017193</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.006300814294502767</v>
+        <v>-0.01119788484995853</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.5389670253156307</v>
+        <v>-0.2562684504179722</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0002584902842268921</v>
+        <v>-0.1353369601300256</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>53.77081141387596</v>
+        <v>66.26551436684881</v>
       </c>
       <c r="B51" t="n">
-        <v>113.3517550136208</v>
+        <v>94.70694952468915</v>
       </c>
       <c r="C51" t="n">
-        <v>45.50087746965555</v>
+        <v>45.50223265440898</v>
       </c>
       <c r="D51" t="n">
-        <v>11.48672855009933</v>
+        <v>10.34958908943175</v>
       </c>
       <c r="E51" t="n">
-        <v>4.845478229771037</v>
+        <v>4.549145238209573</v>
       </c>
       <c r="F51" t="n">
-        <v>5.75818578065141</v>
+        <v>7.2923468310314</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1917615864348316</v>
+        <v>0.08768167415616115</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1665710219033741</v>
+        <v>-0.5497945887850971</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6077336212794707</v>
+        <v>-0.7601042713368399</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.3863544915163225</v>
+        <v>-0.729273847874615</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.01616829160242681</v>
+        <v>-0.01772852644659969</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.2782810856040697</v>
+        <v>-0.371991357751366</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0001949932567883728</v>
+        <v>-0.0004961454242188856</v>
       </c>
     </row>
   </sheetData>
